--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宁南山</t>
+          <t>吃瓜群众</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>20201110</t>
+          <t>20210309</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20201110-国产化,一点也不能放松</t>
+          <t>20210309-中美环保合作,会导致什么</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
+          <t>吃瓜群众/20210309-中美环保合作,会导致什么.html</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201110</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
+          <t>20201110-国产化,一点也不能放松</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
+          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
+          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
+          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
+          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
+          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
+          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
+          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
+          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
+          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>20201201</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
+          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
+          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201201</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
+          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
+          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
+          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
+          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20201212-巨头的使命--从一张中国地图说起</t>
+          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
+          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
+          <t>20201212-巨头的使命--从一张中国地图说起</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
+          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20201220-从两张图看成为发达国家有多难</t>
+          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
+          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
+          <t>20201220-从两张图看成为发达国家有多难</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
+          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20201231-新三线建设与年轻人的希望</t>
+          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
+          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20210101-从2021年初看未来十年的两个三条线</t>
+          <t>20201231-新三线建设与年轻人的希望</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
+          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20210109-另一个国家</t>
+          <t>20210101-从2021年初看未来十年的两个三条线</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>宁南山/20210109-另一个国家.html</t>
+          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
+          <t>20210109-另一个国家</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
+          <t>宁南山/20210109-另一个国家.html</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
+          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
+          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
+          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
+          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
+          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
+          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
+          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
+          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20210207-国产化是漫长的战役</t>
+          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>宁南山/20210207-国产化是漫长的战役.html</t>
+          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -3772,12 +3772,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
+          <t>20210207-国产化是漫长的战役</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
+          <t>宁南山/20210207-国产化是漫长的战役.html</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20210211</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
+          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
+          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210211</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20210218-简单说下2021年预计的几件大事</t>
+          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
+          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
+          <t>20210218-简单说下2021年预计的几件大事</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
+          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
+          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
+          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
+          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
+          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
+          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
+          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20210307-从扶贫,修路到半导体</t>
+          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
+          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>政事堂</t>
+          <t>宁南山</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20201114</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20201114-未来两年经济的确定性与不确定</t>
+          <t>20210307-从扶贫,修路到半导体</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
+          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>20201115</t>
+          <t>20201114</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20201115-RCEP签署,为这一刻准备了30年</t>
+          <t>20201114-未来两年经济的确定性与不确定</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
+          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201115</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
+          <t>20201115-RCEP签署,为这一刻准备了30年</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
+          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>20201117</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20201117-传奇私募被传带走</t>
+          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>政事堂/20201117-传奇私募被传带走.html</t>
+          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4168,20 +4168,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201117</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20201118-莫迪终于给拜登打电话了</t>
+          <t>20201117-传奇私募被传带走</t>
         </is>
       </c>
       <c r="E114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
+          <t>政事堂/20201117-传奇私募被传带走.html</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20201119</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20201119-谁也救不了的'蛋壳'</t>
+          <t>20201118-莫迪终于给拜登打电话了</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
+          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>20201120</t>
+          <t>20201119</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20201120-坐在宝马里面笑的华晨破产了</t>
+          <t>20201119-谁也救不了的'蛋壳'</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
+          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201120</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20201121-中国考虑加入CPTPP的考量</t>
+          <t>20201120-坐在宝马里面笑的华晨破产了</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
+          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>20201122</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20201122-零容忍!金融委发了尚方宝剑</t>
+          <t>20201121-中国考虑加入CPTPP的考量</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
+          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20201123</t>
+          <t>20201122</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20201123-拜登的国务卿布林肯</t>
+          <t>20201122-零容忍!金融委发了尚方宝剑</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
+          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>20201124</t>
+          <t>20201123</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20201124-东京地检调查安倍,这只是开始</t>
+          <t>20201123-拜登的国务卿布林肯</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
+          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20201125</t>
+          <t>20201124</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
+          <t>20201124-东京地检调查安倍,这只是开始</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
+          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20201126</t>
+          <t>20201125</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20201126-投资的抉择</t>
+          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>政事堂/20201126-投资的抉择.html</t>
+          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201126</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20201127-全球即将爆发的'不讲武德'</t>
+          <t>20201126-投资的抉择</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
+          <t>政事堂/20201126-投资的抉择.html</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>20201128</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
+          <t>20201127-全球即将爆发的'不讲武德'</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
+          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201128</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20201129-伊朗刺杀事件中的美国卧底</t>
+          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
+          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20201130</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20201130-马保国凉凉之必然性分析</t>
+          <t>20201129-伊朗刺杀事件中的美国卧底</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
+          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4597,25 +4597,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20201202</t>
+          <t>20201130</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20201202-为何要持续去怼澳大利亚</t>
+          <t>20201130-马保国凉凉之必然性分析</t>
         </is>
       </c>
       <c r="E127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
+          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20201202-关于胡锡进的一则短评</t>
+          <t>20201202-为何要持续去怼澳大利亚</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
+          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4663,20 +4663,20 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>20201203</t>
+          <t>20201202</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20201203-伊万卡成了突破口</t>
+          <t>20201202-关于胡锡进的一则短评</t>
         </is>
       </c>
       <c r="E129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>政事堂/20201203-伊万卡成了突破口.html</t>
+          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20201204</t>
+          <t>20201203</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20201204-中国的舆论阵地要升级了</t>
+          <t>20201203-伊万卡成了突破口</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
+          <t>政事堂/20201203-伊万卡成了突破口.html</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4729,20 +4729,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201204</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
+          <t>20201204-中国的舆论阵地要升级了</t>
         </is>
       </c>
       <c r="E131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
+          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>20201206</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20201206-沃森生物骂战背后的斗争</t>
+          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
         </is>
       </c>
       <c r="E132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
+          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20201207</t>
+          <t>20201206</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20201207-伊朗的刺杀,印度的革命</t>
+          <t>20201206-沃森生物骂战背后的斗争</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
+          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20201208</t>
+          <t>20201207</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
+          <t>20201207-伊朗的刺杀,印度的革命</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
+          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201208</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20201209-宁波假名媛碰上了假富二代</t>
+          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
+          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20201210</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20201210-张近东把苏宁押给了马云</t>
+          <t>20201209-宁波假名媛碰上了假富二代</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
+          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20201211</t>
+          <t>20201210</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
+          <t>20201210-张近东把苏宁押给了马云</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
+          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201211</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20201212-对互联网巨头反垄断的深层理解</t>
+          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
+          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20201213</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20201213-盲盒、卡片与多巴胺</t>
+          <t>20201212-对互联网巨头反垄断的深层理解</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
+          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20201214</t>
+          <t>20201213</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20201214-什么是'需求侧改革'</t>
+          <t>20201213-盲盒、卡片与多巴胺</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
+          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>20201215</t>
+          <t>20201214</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20201215-需求侧改革与内循环</t>
+          <t>20201214-什么是'需求侧改革'</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>政事堂/20201215-需求侧改革与内循环.html</t>
+          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201215</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20201216-中芯的内斗与消费侧的机遇</t>
+          <t>20201215-需求侧改革与内循环</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
+          <t>政事堂/20201215-需求侧改革与内循环.html</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20201217</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20201217-消费侧改革释放的机会</t>
+          <t>20201216-中芯的内斗与消费侧的机遇</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
+          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20201218</t>
+          <t>20201217</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20201218-中央经济工作会议的风向标</t>
+          <t>20201217-消费侧改革释放的机会</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
+          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20201219</t>
+          <t>20201218</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20201219-互联网巨头的至暗时刻</t>
+          <t>20201218-中央经济工作会议的风向标</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
+          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201219</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
+          <t>20201219-互联网巨头的至暗时刻</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
+          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20201221</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20201221-反垄断与反混业经营</t>
+          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>政事堂/20201221-反垄断与反混业经营.html</t>
+          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20201222</t>
+          <t>20201221</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20201222-卸任前,特朗普埋了三个棋子</t>
+          <t>20201221-反垄断与反混业经营</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
+          <t>政事堂/20201221-反垄断与反混业经营.html</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20201223</t>
+          <t>20201222</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20201223-人民日报又提房地产税</t>
+          <t>20201222-卸任前,特朗普埋了三个棋子</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>政事堂/20201223-人民日报又提房地产税.html</t>
+          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20201224</t>
+          <t>20201223</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
+          <t>20201223-人民日报又提房地产税</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
+          <t>政事堂/20201223-人民日报又提房地产税.html</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201224</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20201225-英法中德美,三场胆小鬼游戏</t>
+          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
+          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20201226</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20201226-谁是朋友,谁是敌人</t>
+          <t>20201225-英法中德美,三场胆小鬼游戏</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
+          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20201227</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20201227-反垄断之后,下一步该怎么走</t>
+          <t>20201226-谁是朋友,谁是敌人</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
+          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>20201228</t>
+          <t>20201227</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20201228-下一个二十年</t>
+          <t>20201227-反垄断之后,下一步该怎么走</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>政事堂/20201228-下一个二十年.html</t>
+          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20201229</t>
+          <t>20201228</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20201229-涨价去库存的茅台</t>
+          <t>20201228-下一个二十年</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>政事堂/20201229-涨价去库存的茅台.html</t>
+          <t>政事堂/20201228-下一个二十年.html</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>20201230</t>
+          <t>20201229</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20201230-我们,赢了!</t>
+          <t>20201229-涨价去库存的茅台</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>政事堂/20201230-我们,赢了!.html</t>
+          <t>政事堂/20201229-涨价去库存的茅台.html</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
+          <t>20201230-我们,赢了!</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
+          <t>政事堂/20201230-我们,赢了!.html</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201230</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20201231-2020年就要过去了,我很怀念它</t>
+          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
+          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5658,15 +5658,15 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
+          <t>20201231-2020年就要过去了,我很怀念它</t>
         </is>
       </c>
       <c r="E159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
+          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5686,25 +5686,25 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
+          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
         </is>
       </c>
       <c r="E160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
+          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>20210102</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20210102-山川形便与犬牙相入</t>
+          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
+          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>20210103</t>
+          <t>20210102</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20210103-温莎银枪小霸王</t>
+          <t>20210102-山川形便与犬牙相入</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>政事堂/20210103-温莎银枪小霸王.html</t>
+          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20210104</t>
+          <t>20210103</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
+          <t>20210103-温莎银枪小霸王</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
+          <t>政事堂/20210103-温莎银枪小霸王.html</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20210105</t>
+          <t>20210104</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20210105-拼多多的'临时工'错在哪</t>
+          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
+          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20210106</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20210106-民主党拿下参议院后的影响</t>
+          <t>20210105-拼多多的'临时工'错在哪</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
+          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20210107</t>
+          <t>20210106</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20210107-国会山的陷落</t>
+          <t>20210106-民主党拿下参议院后的影响</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>政事堂/20210107-国会山的陷落.html</t>
+          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>20210108</t>
+          <t>20210107</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20210108-苹果的过去,特斯拉的未来</t>
+          <t>20210107-国会山的陷落</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
+          <t>政事堂/20210107-国会山的陷落.html</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210108</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
+          <t>20210108-苹果的过去,特斯拉的未来</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
+          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20210110-特朗普手机变'砖头'了</t>
+          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
+          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>20210111</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20210111-被'杀人诛心'的特朗普</t>
+          <t>20210110-特朗普手机变'砖头'了</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
+          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>20210112</t>
+          <t>20210111</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20210112-新一轮牛市的怎么走</t>
+          <t>20210111-被'杀人诛心'的特朗普</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
+          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20210113</t>
+          <t>20210112</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20210113-马斯克与Paypal的借道入华</t>
+          <t>20210112-新一轮牛市的怎么走</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
+          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>20210114</t>
+          <t>20210113</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20210114-一杯特殊的星巴克</t>
+          <t>20210113-马斯克与Paypal的借道入华</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
+          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20210115-中国迎来了一位女对手</t>
+          <t>20210114-一杯特殊的星巴克</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
+          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>20210116</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20210116-无偿转让好,酱香来养老</t>
+          <t>20210115-中国迎来了一位女对手</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
+          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210116</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20210117-两位'小公主'的逆行之旅</t>
+          <t>20210116-无偿转让好,酱香来养老</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
+          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20210118</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20210118-三星太子当庭被捕</t>
+          <t>20210117-两位'小公主'的逆行之旅</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>政事堂/20210118-三星太子当庭被捕.html</t>
+          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>20210119</t>
+          <t>20210118</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20210119-表演大师武契奇</t>
+          <t>20210118-三星太子当庭被捕</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>政事堂/20210119-表演大师武契奇.html</t>
+          <t>政事堂/20210118-三星太子当庭被捕.html</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>20210120</t>
+          <t>20210119</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20210120-告别特朗普</t>
+          <t>20210119-表演大师武契奇</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>政事堂/20210120-告别特朗普.html</t>
+          <t>政事堂/20210119-表演大师武契奇.html</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>20210121</t>
+          <t>20210120</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20210121-28人制裁名单,中国送别特朗普</t>
+          <t>20210120-告别特朗普</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
+          <t>政事堂/20210120-告别特朗普.html</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>20210122</t>
+          <t>20210121</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20210122-从上海飙升的房价聊起</t>
+          <t>20210121-28人制裁名单,中国送别特朗普</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
+          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210122</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20210123-走向新时代</t>
+          <t>20210122-从上海飙升的房价聊起</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>政事堂/20210123-走向新时代.html</t>
+          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>20210124</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
+          <t>20210123-走向新时代</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
+          <t>政事堂/20210123-走向新时代.html</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>20210125</t>
+          <t>20210124</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20210125-贾跃亭向左,许家印向右</t>
+          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
+          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6511,20 +6511,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>20210126</t>
+          <t>20210125</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20210126-学术圈为何不能反垄断</t>
+          <t>20210125-贾跃亭向左,许家印向右</t>
         </is>
       </c>
       <c r="E185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
+          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6544,20 +6544,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>20210127</t>
+          <t>20210126</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20210127-废柴们如何收割华尔街大佬</t>
+          <t>20210126-学术圈为何不能反垄断</t>
         </is>
       </c>
       <c r="E186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
+          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20210128</t>
+          <t>20210127</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20210128-资本割韭菜的套路</t>
+          <t>20210127-废柴们如何收割华尔街大佬</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>政事堂/20210128-资本割韭菜的套路.html</t>
+          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>20210129</t>
+          <t>20210128</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20210129-从海航破产说起</t>
+          <t>20210128-资本割韭菜的套路</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>政事堂/20210129-从海航破产说起.html</t>
+          <t>政事堂/20210128-资本割韭菜的套路.html</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>20210130</t>
+          <t>20210129</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
+          <t>20210129-从海航破产说起</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
+          <t>政事堂/20210129-从海航破产说起.html</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210130</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20210131-基金要变天了......</t>
+          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>政事堂/20210131-基金要变天了.......html</t>
+          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>20210201</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20210201-缅甸政变,下一步呢</t>
+          <t>20210131-基金要变天了......</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
+          <t>政事堂/20210131-基金要变天了.......html</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>20210202</t>
+          <t>20210201</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20210202-调控背后的定价权之争</t>
+          <t>20210201-缅甸政变,下一步呢</t>
         </is>
       </c>
       <c r="E192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>政事堂/20210202-调控背后的定价权之争.html</t>
+          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -6775,20 +6775,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>20210203</t>
+          <t>20210202</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20210203-告别人人影视</t>
+          <t>20210202-调控背后的定价权之争</t>
         </is>
       </c>
       <c r="E193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>政事堂/20210203-告别人人影视.html</t>
+          <t>政事堂/20210202-调控背后的定价权之争.html</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>20210204</t>
+          <t>20210203</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20210204-短视频的机制</t>
+          <t>20210203-告别人人影视</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>政事堂/20210204-短视频的机制.html</t>
+          <t>政事堂/20210203-告别人人影视.html</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20210205</t>
+          <t>20210204</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20210205-拜登的外交与A股的改革</t>
+          <t>20210204-短视频的机制</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
+          <t>政事堂/20210204-短视频的机制.html</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>20210206</t>
+          <t>20210205</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20210206-漫谈影视文化的知识产权与垄断</t>
+          <t>20210205-拜登的外交与A股的改革</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
+          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6907,20 +6907,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210206</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
+          <t>20210206-漫谈影视文化的知识产权与垄断</t>
         </is>
       </c>
       <c r="E197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
+          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6940,20 +6940,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>20210208</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20210208-知识产权秩序与短视频革命</t>
+          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
         </is>
       </c>
       <c r="E198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
+          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210208</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20210210-拼团的名媛与美国的航母</t>
+          <t>20210208-知识产权秩序与短视频革命</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
+          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7006,20 +7006,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>20210212</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20210212-牛年的新秩序</t>
+          <t>20210210-拼团的名媛与美国的航母</t>
         </is>
       </c>
       <c r="E200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>政事堂/20210212-牛年的新秩序.html</t>
+          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7039,20 +7039,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>20210213</t>
+          <t>20210212</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20210213-马斯克的神化与革命</t>
+          <t>20210212-牛年的新秩序</t>
         </is>
       </c>
       <c r="E201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>政事堂/20210213-马斯克的神化与革命.html</t>
+          <t>政事堂/20210212-牛年的新秩序.html</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7072,20 +7072,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>20210215</t>
+          <t>20210213</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20210215-低生育率的原因</t>
+          <t>20210213-马斯克的神化与革命</t>
         </is>
       </c>
       <c r="E202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>政事堂/20210215-低生育率的原因.html</t>
+          <t>政事堂/20210213-马斯克的神化与革命.html</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>20210216</t>
+          <t>20210215</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20210216-一代版本一代神</t>
+          <t>20210215-低生育率的原因</t>
         </is>
       </c>
       <c r="E203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>政事堂/20210216-一代版本一代神.html</t>
+          <t>政事堂/20210215-低生育率的原因.html</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>20210217</t>
+          <t>20210216</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20210217-马斯克、宗教与黑客帝国</t>
+          <t>20210216-一代版本一代神</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
+          <t>政事堂/20210216-一代版本一代神.html</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210217</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20210218-品酒师入围院士,在侮辱谁</t>
+          <t>20210217-马斯克、宗教与黑客帝国</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
+          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>20210219</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
+          <t>20210218-品酒师入围院士,在侮辱谁</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
+          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7237,20 +7237,20 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210219</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20210221-应该用《英烈法》保护我们的英雄</t>
+          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
         </is>
       </c>
       <c r="E207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
+          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7275,15 +7275,15 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20210221-资本大佬们又要回来了</t>
+          <t>20210221-应该用《英烈法》保护我们的英雄</t>
         </is>
       </c>
       <c r="E208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
+          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>20210223</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20210223-抱团基金的走向</t>
+          <t>20210221-资本大佬们又要回来了</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>政事堂/20210223-抱团基金的走向.html</t>
+          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>20210224</t>
+          <t>20210223</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20210224-印花税打崩了抱团基金</t>
+          <t>20210223-抱团基金的走向</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
+          <t>政事堂/20210223-抱团基金的走向.html</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>20210225</t>
+          <t>20210224</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
+          <t>20210224-印花税打崩了抱团基金</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
+          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20210225-马斯克VS神,巨头的归来</t>
+          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
+          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210225</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20210226-不讲武德,拜登突袭叙利亚</t>
+          <t>20210225-马斯克VS神,巨头的归来</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
+          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>20210227</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20210227-'第一村'的华西垮不了</t>
+          <t>20210226-不讲武德,拜登突袭叙利亚</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
+          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>20210228</t>
+          <t>20210227</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20210228-'大空头'巴菲特的唱空</t>
+          <t>20210227-'第一村'的华西垮不了</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
+          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210228</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20210301-凤梨与稀土</t>
+          <t>20210228-'大空头'巴菲特的唱空</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -7547,12 +7547,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>政事堂/20210301-凤梨与稀土.html</t>
+          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20210302</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20210302-'口头加息'与'进一步加征印花税'</t>
+          <t>20210301-凤梨与稀土</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
+          <t>政事堂/20210301-凤梨与稀土.html</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7600,20 +7600,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210302</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20210303-破局：从世界工厂到世界发动机</t>
+          <t>20210302-'口头加息'与'进一步加征印花税'</t>
         </is>
       </c>
       <c r="E218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
+          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7633,20 +7633,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>20210304</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20210304-炒币与X茅的起源</t>
+          <t>20210303-破局：从世界工厂到世界发动机</t>
         </is>
       </c>
       <c r="E219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>政事堂/20210304-炒币与X茅的起源.html</t>
+          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7666,20 +7666,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>20210305</t>
+          <t>20210304</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20210305-阳谋推恩令</t>
+          <t>20210304-炒币与X茅的起源</t>
         </is>
       </c>
       <c r="E220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>政事堂/20210305-阳谋推恩令.html</t>
+          <t>政事堂/20210304-炒币与X茅的起源.html</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -7699,20 +7699,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>20210306</t>
+          <t>20210305</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20210306-拜登、白酒与新能源</t>
+          <t>20210305-阳谋推恩令</t>
         </is>
       </c>
       <c r="E221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
+          <t>政事堂/20210305-阳谋推恩令.html</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210306</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20210307-拜登、旧巨头与新神</t>
+          <t>20210306-拜登、白酒与新能源</t>
         </is>
       </c>
       <c r="E222" t="b">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
+          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7765,23 +7765,89 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
+          <t>20210307</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>20210307-拜登、旧巨头与新神</t>
+        </is>
+      </c>
+      <c r="E223" t="b">
+        <v>1</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
           <t>20210308</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
         </is>
       </c>
-      <c r="E223" t="b">
+      <c r="E224" t="b">
+        <v>1</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>20210309</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>20210309-救市的国家队与撤退的集结号</t>
+        </is>
+      </c>
+      <c r="E225" t="b">
         <v>0</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
         <is>
           <t>202103</t>
         </is>

--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3074,17 +3074,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>宁南山</t>
+          <t>吃瓜群众</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>20201110</t>
+          <t>20210310</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20201110-国产化,一点也不能放松</t>
+          <t>20210310-普京的接班人,已经定了</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
+          <t>吃瓜群众/20210310-普京的接班人,已经定了.html</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201110</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
+          <t>20201110-国产化,一点也不能放松</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
+          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
+          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
+          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
+          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
+          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
+          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
+          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
+          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
+          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>20201201</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
+          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
+          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201201</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
+          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
+          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
+          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
+          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20201212-巨头的使命--从一张中国地图说起</t>
+          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
+          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
+          <t>20201212-巨头的使命--从一张中国地图说起</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
+          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20201220-从两张图看成为发达国家有多难</t>
+          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
+          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
+          <t>20201220-从两张图看成为发达国家有多难</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
+          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20201231-新三线建设与年轻人的希望</t>
+          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
+          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20210101-从2021年初看未来十年的两个三条线</t>
+          <t>20201231-新三线建设与年轻人的希望</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
+          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20210109-另一个国家</t>
+          <t>20210101-从2021年初看未来十年的两个三条线</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>宁南山/20210109-另一个国家.html</t>
+          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
+          <t>20210109-另一个国家</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
+          <t>宁南山/20210109-另一个国家.html</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
+          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
+          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
+          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
+          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
+          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
+          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
+          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
+          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20210207-国产化是漫长的战役</t>
+          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>宁南山/20210207-国产化是漫长的战役.html</t>
+          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
+          <t>20210207-国产化是漫长的战役</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
+          <t>宁南山/20210207-国产化是漫长的战役.html</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20210211</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
+          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
+          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210211</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20210218-简单说下2021年预计的几件大事</t>
+          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
+          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
+          <t>20210218-简单说下2021年预计的几件大事</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
+          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
+          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
+          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
+          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
+          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
+          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
+          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20210307-从扶贫,修路到半导体</t>
+          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
+          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4064,17 +4064,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>政事堂</t>
+          <t>宁南山</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>20201114</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20201114-未来两年经济的确定性与不确定</t>
+          <t>20210307-从扶贫,修路到半导体</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4082,12 +4082,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
+          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20201115</t>
+          <t>20201114</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20201115-RCEP签署,为这一刻准备了30年</t>
+          <t>20201114-未来两年经济的确定性与不确定</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
+          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201115</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
+          <t>20201115-RCEP签署,为这一刻准备了30年</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
+          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20201117</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20201117-传奇私募被传带走</t>
+          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>政事堂/20201117-传奇私募被传带走.html</t>
+          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4201,20 +4201,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201117</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20201118-莫迪终于给拜登打电话了</t>
+          <t>20201117-传奇私募被传带走</t>
         </is>
       </c>
       <c r="E115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
+          <t>政事堂/20201117-传奇私募被传带走.html</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>20201119</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20201119-谁也救不了的'蛋壳'</t>
+          <t>20201118-莫迪终于给拜登打电话了</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
+          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>20201120</t>
+          <t>20201119</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20201120-坐在宝马里面笑的华晨破产了</t>
+          <t>20201119-谁也救不了的'蛋壳'</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
+          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201120</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20201121-中国考虑加入CPTPP的考量</t>
+          <t>20201120-坐在宝马里面笑的华晨破产了</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
+          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20201122</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20201122-零容忍!金融委发了尚方宝剑</t>
+          <t>20201121-中国考虑加入CPTPP的考量</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
+          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>20201123</t>
+          <t>20201122</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20201123-拜登的国务卿布林肯</t>
+          <t>20201122-零容忍!金融委发了尚方宝剑</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
+          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20201124</t>
+          <t>20201123</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20201124-东京地检调查安倍,这只是开始</t>
+          <t>20201123-拜登的国务卿布林肯</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
+          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20201125</t>
+          <t>20201124</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
+          <t>20201124-东京地检调查安倍,这只是开始</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
+          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>20201126</t>
+          <t>20201125</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20201126-投资的抉择</t>
+          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>政事堂/20201126-投资的抉择.html</t>
+          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201126</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20201127-全球即将爆发的'不讲武德'</t>
+          <t>20201126-投资的抉择</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
+          <t>政事堂/20201126-投资的抉择.html</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20201128</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
+          <t>20201127-全球即将爆发的'不讲武德'</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
+          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201128</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20201129-伊朗刺杀事件中的美国卧底</t>
+          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
+          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20201130</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20201130-马保国凉凉之必然性分析</t>
+          <t>20201129-伊朗刺杀事件中的美国卧底</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
+          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4630,25 +4630,25 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>20201202</t>
+          <t>20201130</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20201202-为何要持续去怼澳大利亚</t>
+          <t>20201130-马保国凉凉之必然性分析</t>
         </is>
       </c>
       <c r="E128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
+          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20201202-关于胡锡进的一则短评</t>
+          <t>20201202-为何要持续去怼澳大利亚</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
+          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4696,20 +4696,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20201203</t>
+          <t>20201202</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20201203-伊万卡成了突破口</t>
+          <t>20201202-关于胡锡进的一则短评</t>
         </is>
       </c>
       <c r="E130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>政事堂/20201203-伊万卡成了突破口.html</t>
+          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20201204</t>
+          <t>20201203</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20201204-中国的舆论阵地要升级了</t>
+          <t>20201203-伊万卡成了突破口</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
+          <t>政事堂/20201203-伊万卡成了突破口.html</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201204</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
+          <t>20201204-中国的舆论阵地要升级了</t>
         </is>
       </c>
       <c r="E132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
+          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4795,20 +4795,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20201206</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20201206-沃森生物骂战背后的斗争</t>
+          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
         </is>
       </c>
       <c r="E133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
+          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20201207</t>
+          <t>20201206</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20201207-伊朗的刺杀,印度的革命</t>
+          <t>20201206-沃森生物骂战背后的斗争</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
+          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20201208</t>
+          <t>20201207</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
+          <t>20201207-伊朗的刺杀,印度的革命</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
+          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201208</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20201209-宁波假名媛碰上了假富二代</t>
+          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
+          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20201210</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20201210-张近东把苏宁押给了马云</t>
+          <t>20201209-宁波假名媛碰上了假富二代</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
+          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20201211</t>
+          <t>20201210</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
+          <t>20201210-张近东把苏宁押给了马云</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
+          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201211</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20201212-对互联网巨头反垄断的深层理解</t>
+          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
+          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20201213</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20201213-盲盒、卡片与多巴胺</t>
+          <t>20201212-对互联网巨头反垄断的深层理解</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
+          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>20201214</t>
+          <t>20201213</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20201214-什么是'需求侧改革'</t>
+          <t>20201213-盲盒、卡片与多巴胺</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
+          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20201215</t>
+          <t>20201214</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20201215-需求侧改革与内循环</t>
+          <t>20201214-什么是'需求侧改革'</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>政事堂/20201215-需求侧改革与内循环.html</t>
+          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201215</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20201216-中芯的内斗与消费侧的机遇</t>
+          <t>20201215-需求侧改革与内循环</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
+          <t>政事堂/20201215-需求侧改革与内循环.html</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20201217</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20201217-消费侧改革释放的机会</t>
+          <t>20201216-中芯的内斗与消费侧的机遇</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
+          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20201218</t>
+          <t>20201217</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20201218-中央经济工作会议的风向标</t>
+          <t>20201217-消费侧改革释放的机会</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
+          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20201219</t>
+          <t>20201218</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20201219-互联网巨头的至暗时刻</t>
+          <t>20201218-中央经济工作会议的风向标</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
+          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201219</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
+          <t>20201219-互联网巨头的至暗时刻</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
+          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20201221</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20201221-反垄断与反混业经营</t>
+          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>政事堂/20201221-反垄断与反混业经营.html</t>
+          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20201222</t>
+          <t>20201221</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20201222-卸任前,特朗普埋了三个棋子</t>
+          <t>20201221-反垄断与反混业经营</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
+          <t>政事堂/20201221-反垄断与反混业经营.html</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20201223</t>
+          <t>20201222</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20201223-人民日报又提房地产税</t>
+          <t>20201222-卸任前,特朗普埋了三个棋子</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>政事堂/20201223-人民日报又提房地产税.html</t>
+          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20201224</t>
+          <t>20201223</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
+          <t>20201223-人民日报又提房地产税</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
+          <t>政事堂/20201223-人民日报又提房地产税.html</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201224</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20201225-英法中德美,三场胆小鬼游戏</t>
+          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
+          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20201226</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20201226-谁是朋友,谁是敌人</t>
+          <t>20201225-英法中德美,三场胆小鬼游戏</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
+          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>20201227</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20201227-反垄断之后,下一步该怎么走</t>
+          <t>20201226-谁是朋友,谁是敌人</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
+          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20201228</t>
+          <t>20201227</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20201228-下一个二十年</t>
+          <t>20201227-反垄断之后,下一步该怎么走</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>政事堂/20201228-下一个二十年.html</t>
+          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>20201229</t>
+          <t>20201228</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20201229-涨价去库存的茅台</t>
+          <t>20201228-下一个二十年</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>政事堂/20201229-涨价去库存的茅台.html</t>
+          <t>政事堂/20201228-下一个二十年.html</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>20201230</t>
+          <t>20201229</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20201230-我们,赢了!</t>
+          <t>20201229-涨价去库存的茅台</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>政事堂/20201230-我们,赢了!.html</t>
+          <t>政事堂/20201229-涨价去库存的茅台.html</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
+          <t>20201230-我们,赢了!</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
+          <t>政事堂/20201230-我们,赢了!.html</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201230</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20201231-2020年就要过去了,我很怀念它</t>
+          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
+          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5691,15 +5691,15 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
+          <t>20201231-2020年就要过去了,我很怀念它</t>
         </is>
       </c>
       <c r="E160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
+          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5719,25 +5719,25 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
+          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
         </is>
       </c>
       <c r="E161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
+          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>20210102</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20210102-山川形便与犬牙相入</t>
+          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
+          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20210103</t>
+          <t>20210102</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20210103-温莎银枪小霸王</t>
+          <t>20210102-山川形便与犬牙相入</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>政事堂/20210103-温莎银枪小霸王.html</t>
+          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20210104</t>
+          <t>20210103</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
+          <t>20210103-温莎银枪小霸王</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
+          <t>政事堂/20210103-温莎银枪小霸王.html</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20210105</t>
+          <t>20210104</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20210105-拼多多的'临时工'错在哪</t>
+          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
+          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20210106</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20210106-民主党拿下参议院后的影响</t>
+          <t>20210105-拼多多的'临时工'错在哪</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
+          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>20210107</t>
+          <t>20210106</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20210107-国会山的陷落</t>
+          <t>20210106-民主党拿下参议院后的影响</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>政事堂/20210107-国会山的陷落.html</t>
+          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>20210108</t>
+          <t>20210107</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20210108-苹果的过去,特斯拉的未来</t>
+          <t>20210107-国会山的陷落</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
+          <t>政事堂/20210107-国会山的陷落.html</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210108</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
+          <t>20210108-苹果的过去,特斯拉的未来</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
+          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20210110-特朗普手机变'砖头'了</t>
+          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
+          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>20210111</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20210111-被'杀人诛心'的特朗普</t>
+          <t>20210110-特朗普手机变'砖头'了</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
+          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20210112</t>
+          <t>20210111</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20210112-新一轮牛市的怎么走</t>
+          <t>20210111-被'杀人诛心'的特朗普</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
+          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>20210113</t>
+          <t>20210112</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20210113-马斯克与Paypal的借道入华</t>
+          <t>20210112-新一轮牛市的怎么走</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
+          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>20210114</t>
+          <t>20210113</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20210114-一杯特殊的星巴克</t>
+          <t>20210113-马斯克与Paypal的借道入华</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
+          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20210115-中国迎来了一位女对手</t>
+          <t>20210114-一杯特殊的星巴克</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
+          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>20210116</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20210116-无偿转让好,酱香来养老</t>
+          <t>20210115-中国迎来了一位女对手</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
+          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210116</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20210117-两位'小公主'的逆行之旅</t>
+          <t>20210116-无偿转让好,酱香来养老</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
+          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>20210118</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20210118-三星太子当庭被捕</t>
+          <t>20210117-两位'小公主'的逆行之旅</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>政事堂/20210118-三星太子当庭被捕.html</t>
+          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>20210119</t>
+          <t>20210118</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20210119-表演大师武契奇</t>
+          <t>20210118-三星太子当庭被捕</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>政事堂/20210119-表演大师武契奇.html</t>
+          <t>政事堂/20210118-三星太子当庭被捕.html</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>20210120</t>
+          <t>20210119</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20210120-告别特朗普</t>
+          <t>20210119-表演大师武契奇</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>政事堂/20210120-告别特朗普.html</t>
+          <t>政事堂/20210119-表演大师武契奇.html</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>20210121</t>
+          <t>20210120</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20210121-28人制裁名单,中国送别特朗普</t>
+          <t>20210120-告别特朗普</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
+          <t>政事堂/20210120-告别特朗普.html</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>20210122</t>
+          <t>20210121</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20210122-从上海飙升的房价聊起</t>
+          <t>20210121-28人制裁名单,中国送别特朗普</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
+          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210122</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20210123-走向新时代</t>
+          <t>20210122-从上海飙升的房价聊起</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>政事堂/20210123-走向新时代.html</t>
+          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>20210124</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
+          <t>20210123-走向新时代</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
+          <t>政事堂/20210123-走向新时代.html</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>20210125</t>
+          <t>20210124</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20210125-贾跃亭向左,许家印向右</t>
+          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
+          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6544,20 +6544,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>20210126</t>
+          <t>20210125</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20210126-学术圈为何不能反垄断</t>
+          <t>20210125-贾跃亭向左,许家印向右</t>
         </is>
       </c>
       <c r="E186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
+          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6577,20 +6577,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20210127</t>
+          <t>20210126</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20210127-废柴们如何收割华尔街大佬</t>
+          <t>20210126-学术圈为何不能反垄断</t>
         </is>
       </c>
       <c r="E187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
+          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>20210128</t>
+          <t>20210127</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20210128-资本割韭菜的套路</t>
+          <t>20210127-废柴们如何收割华尔街大佬</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>政事堂/20210128-资本割韭菜的套路.html</t>
+          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>20210129</t>
+          <t>20210128</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20210129-从海航破产说起</t>
+          <t>20210128-资本割韭菜的套路</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>政事堂/20210129-从海航破产说起.html</t>
+          <t>政事堂/20210128-资本割韭菜的套路.html</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>20210130</t>
+          <t>20210129</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
+          <t>20210129-从海航破产说起</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
+          <t>政事堂/20210129-从海航破产说起.html</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210130</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20210131-基金要变天了......</t>
+          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>政事堂/20210131-基金要变天了.......html</t>
+          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>20210201</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20210201-缅甸政变,下一步呢</t>
+          <t>20210131-基金要变天了......</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
+          <t>政事堂/20210131-基金要变天了.......html</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>20210202</t>
+          <t>20210201</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20210202-调控背后的定价权之争</t>
+          <t>20210201-缅甸政变,下一步呢</t>
         </is>
       </c>
       <c r="E193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>政事堂/20210202-调控背后的定价权之争.html</t>
+          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6808,20 +6808,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>20210203</t>
+          <t>20210202</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20210203-告别人人影视</t>
+          <t>20210202-调控背后的定价权之争</t>
         </is>
       </c>
       <c r="E194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>政事堂/20210203-告别人人影视.html</t>
+          <t>政事堂/20210202-调控背后的定价权之争.html</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20210204</t>
+          <t>20210203</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20210204-短视频的机制</t>
+          <t>20210203-告别人人影视</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>政事堂/20210204-短视频的机制.html</t>
+          <t>政事堂/20210203-告别人人影视.html</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>20210205</t>
+          <t>20210204</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20210205-拜登的外交与A股的改革</t>
+          <t>20210204-短视频的机制</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
+          <t>政事堂/20210204-短视频的机制.html</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>20210206</t>
+          <t>20210205</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20210206-漫谈影视文化的知识产权与垄断</t>
+          <t>20210205-拜登的外交与A股的改革</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
+          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6940,20 +6940,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210206</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
+          <t>20210206-漫谈影视文化的知识产权与垄断</t>
         </is>
       </c>
       <c r="E198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
+          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6973,20 +6973,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>20210208</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20210208-知识产权秩序与短视频革命</t>
+          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
         </is>
       </c>
       <c r="E199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
+          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210208</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20210210-拼团的名媛与美国的航母</t>
+          <t>20210208-知识产权秩序与短视频革命</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
+          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7039,20 +7039,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>20210212</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20210212-牛年的新秩序</t>
+          <t>20210210-拼团的名媛与美国的航母</t>
         </is>
       </c>
       <c r="E201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>政事堂/20210212-牛年的新秩序.html</t>
+          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7072,20 +7072,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>20210213</t>
+          <t>20210212</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20210213-马斯克的神化与革命</t>
+          <t>20210212-牛年的新秩序</t>
         </is>
       </c>
       <c r="E202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>政事堂/20210213-马斯克的神化与革命.html</t>
+          <t>政事堂/20210212-牛年的新秩序.html</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>20210215</t>
+          <t>20210213</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20210215-低生育率的原因</t>
+          <t>20210213-马斯克的神化与革命</t>
         </is>
       </c>
       <c r="E203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>政事堂/20210215-低生育率的原因.html</t>
+          <t>政事堂/20210213-马斯克的神化与革命.html</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7138,20 +7138,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>20210216</t>
+          <t>20210215</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20210216-一代版本一代神</t>
+          <t>20210215-低生育率的原因</t>
         </is>
       </c>
       <c r="E204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>政事堂/20210216-一代版本一代神.html</t>
+          <t>政事堂/20210215-低生育率的原因.html</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>20210217</t>
+          <t>20210216</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20210217-马斯克、宗教与黑客帝国</t>
+          <t>20210216-一代版本一代神</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
+          <t>政事堂/20210216-一代版本一代神.html</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210217</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20210218-品酒师入围院士,在侮辱谁</t>
+          <t>20210217-马斯克、宗教与黑客帝国</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
+          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>20210219</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
+          <t>20210218-品酒师入围院士,在侮辱谁</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
+          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7270,20 +7270,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210219</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20210221-应该用《英烈法》保护我们的英雄</t>
+          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
         </is>
       </c>
       <c r="E208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
+          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7308,15 +7308,15 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20210221-资本大佬们又要回来了</t>
+          <t>20210221-应该用《英烈法》保护我们的英雄</t>
         </is>
       </c>
       <c r="E209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
+          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>20210223</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20210223-抱团基金的走向</t>
+          <t>20210221-资本大佬们又要回来了</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>政事堂/20210223-抱团基金的走向.html</t>
+          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>20210224</t>
+          <t>20210223</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20210224-印花税打崩了抱团基金</t>
+          <t>20210223-抱团基金的走向</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
+          <t>政事堂/20210223-抱团基金的走向.html</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>20210225</t>
+          <t>20210224</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
+          <t>20210224-印花税打崩了抱团基金</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
+          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20210225-马斯克VS神,巨头的归来</t>
+          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
+          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210225</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20210226-不讲武德,拜登突袭叙利亚</t>
+          <t>20210225-马斯克VS神,巨头的归来</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
+          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>20210227</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20210227-'第一村'的华西垮不了</t>
+          <t>20210226-不讲武德,拜登突袭叙利亚</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
+          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>20210228</t>
+          <t>20210227</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20210228-'大空头'巴菲特的唱空</t>
+          <t>20210227-'第一村'的华西垮不了</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
+          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210228</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20210301-凤梨与稀土</t>
+          <t>20210228-'大空头'巴菲特的唱空</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>政事堂/20210301-凤梨与稀土.html</t>
+          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>20210302</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20210302-'口头加息'与'进一步加征印花税'</t>
+          <t>20210301-凤梨与稀土</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
+          <t>政事堂/20210301-凤梨与稀土.html</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7633,20 +7633,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210302</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20210303-破局：从世界工厂到世界发动机</t>
+          <t>20210302-'口头加息'与'进一步加征印花税'</t>
         </is>
       </c>
       <c r="E219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
+          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7666,20 +7666,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>20210304</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20210304-炒币与X茅的起源</t>
+          <t>20210303-破局：从世界工厂到世界发动机</t>
         </is>
       </c>
       <c r="E220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>政事堂/20210304-炒币与X茅的起源.html</t>
+          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -7699,20 +7699,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>20210305</t>
+          <t>20210304</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20210305-阳谋推恩令</t>
+          <t>20210304-炒币与X茅的起源</t>
         </is>
       </c>
       <c r="E221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>政事堂/20210305-阳谋推恩令.html</t>
+          <t>政事堂/20210304-炒币与X茅的起源.html</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7732,20 +7732,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>20210306</t>
+          <t>20210305</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20210306-拜登、白酒与新能源</t>
+          <t>20210305-阳谋推恩令</t>
         </is>
       </c>
       <c r="E222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
+          <t>政事堂/20210305-阳谋推恩令.html</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210306</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20210307-拜登、旧巨头与新神</t>
+          <t>20210306-拜登、白酒与新能源</t>
         </is>
       </c>
       <c r="E223" t="b">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
+          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>20210308</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
+          <t>20210307-拜登、旧巨头与新神</t>
         </is>
       </c>
       <c r="E224" t="b">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
+          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -7831,23 +7831,89 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
+          <t>20210308</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
+        </is>
+      </c>
+      <c r="E225" t="b">
+        <v>1</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
           <t>20210309</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>20210309-救市的国家队与撤退的集结号</t>
         </is>
       </c>
-      <c r="E225" t="b">
+      <c r="E226" t="b">
+        <v>1</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>20210310</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>20210310-中美的阿拉斯加会谈</t>
+        </is>
+      </c>
+      <c r="E227" t="b">
         <v>0</v>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>政事堂/20210310-中美的阿拉斯加会谈.html</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
         <is>
           <t>202103</t>
         </is>

--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="E81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3107,17 +3107,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>宁南山</t>
+          <t>吃瓜群众</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>20201110</t>
+          <t>20210311</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20201110-国产化,一点也不能放松</t>
+          <t>20210311-魔鬼藏在细节,逻辑还原真相!中美阿拉斯加会谈</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
+          <t>吃瓜群众/20210311-魔鬼藏在细节,逻辑还原真相!中美阿拉斯加会谈.html</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201110</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
+          <t>20201110-国产化,一点也不能放松</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
+          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
+          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
+          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
+          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
+          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
+          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
+          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
+          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
+          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>20201201</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
+          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
+          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201201</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
+          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
+          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
+          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
+          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20201212-巨头的使命--从一张中国地图说起</t>
+          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
+          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
+          <t>20201212-巨头的使命--从一张中国地图说起</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
+          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20201220-从两张图看成为发达国家有多难</t>
+          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
+          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
+          <t>20201220-从两张图看成为发达国家有多难</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
+          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20201231-新三线建设与年轻人的希望</t>
+          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
+          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20210101-从2021年初看未来十年的两个三条线</t>
+          <t>20201231-新三线建设与年轻人的希望</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
+          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20210109-另一个国家</t>
+          <t>20210101-从2021年初看未来十年的两个三条线</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>宁南山/20210109-另一个国家.html</t>
+          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
+          <t>20210109-另一个国家</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
+          <t>宁南山/20210109-另一个国家.html</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
+          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
+          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
+          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
+          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
+          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
+          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
+          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
+          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20210207-国产化是漫长的战役</t>
+          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>宁南山/20210207-国产化是漫长的战役.html</t>
+          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
+          <t>20210207-国产化是漫长的战役</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
+          <t>宁南山/20210207-国产化是漫长的战役.html</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20210211</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
+          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
+          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210211</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20210218-简单说下2021年预计的几件大事</t>
+          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
+          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
+          <t>20210218-简单说下2021年预计的几件大事</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
+          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
+          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
+          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
+          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
+          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
+          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
+          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20210307-从扶贫,修路到半导体</t>
+          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
+          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4097,17 +4097,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>政事堂</t>
+          <t>宁南山</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20201114</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20201114-未来两年经济的确定性与不确定</t>
+          <t>20210307-从扶贫,修路到半导体</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
+          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>20201115</t>
+          <t>20201114</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20201115-RCEP签署,为这一刻准备了30年</t>
+          <t>20201114-未来两年经济的确定性与不确定</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
+          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201115</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
+          <t>20201115-RCEP签署,为这一刻准备了30年</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
+          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20201117</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20201117-传奇私募被传带走</t>
+          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>政事堂/20201117-传奇私募被传带走.html</t>
+          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4234,20 +4234,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201117</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20201118-莫迪终于给拜登打电话了</t>
+          <t>20201117-传奇私募被传带走</t>
         </is>
       </c>
       <c r="E116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
+          <t>政事堂/20201117-传奇私募被传带走.html</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>20201119</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20201119-谁也救不了的'蛋壳'</t>
+          <t>20201118-莫迪终于给拜登打电话了</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
+          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>20201120</t>
+          <t>20201119</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20201120-坐在宝马里面笑的华晨破产了</t>
+          <t>20201119-谁也救不了的'蛋壳'</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
+          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201120</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20201121-中国考虑加入CPTPP的考量</t>
+          <t>20201120-坐在宝马里面笑的华晨破产了</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
+          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>20201122</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20201122-零容忍!金融委发了尚方宝剑</t>
+          <t>20201121-中国考虑加入CPTPP的考量</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
+          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20201123</t>
+          <t>20201122</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20201123-拜登的国务卿布林肯</t>
+          <t>20201122-零容忍!金融委发了尚方宝剑</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
+          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20201124</t>
+          <t>20201123</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20201124-东京地检调查安倍,这只是开始</t>
+          <t>20201123-拜登的国务卿布林肯</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
+          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>20201125</t>
+          <t>20201124</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
+          <t>20201124-东京地检调查安倍,这只是开始</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
+          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>20201126</t>
+          <t>20201125</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20201126-投资的抉择</t>
+          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>政事堂/20201126-投资的抉择.html</t>
+          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201126</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20201127-全球即将爆发的'不讲武德'</t>
+          <t>20201126-投资的抉择</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
+          <t>政事堂/20201126-投资的抉择.html</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20201128</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
+          <t>20201127-全球即将爆发的'不讲武德'</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
+          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201128</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20201129-伊朗刺杀事件中的美国卧底</t>
+          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
+          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>20201130</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20201130-马保国凉凉之必然性分析</t>
+          <t>20201129-伊朗刺杀事件中的美国卧底</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
+          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4663,25 +4663,25 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>20201202</t>
+          <t>20201130</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20201202-为何要持续去怼澳大利亚</t>
+          <t>20201130-马保国凉凉之必然性分析</t>
         </is>
       </c>
       <c r="E129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
+          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20201202-关于胡锡进的一则短评</t>
+          <t>20201202-为何要持续去怼澳大利亚</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
+          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4729,20 +4729,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20201203</t>
+          <t>20201202</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20201203-伊万卡成了突破口</t>
+          <t>20201202-关于胡锡进的一则短评</t>
         </is>
       </c>
       <c r="E131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>政事堂/20201203-伊万卡成了突破口.html</t>
+          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>20201204</t>
+          <t>20201203</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20201204-中国的舆论阵地要升级了</t>
+          <t>20201203-伊万卡成了突破口</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
+          <t>政事堂/20201203-伊万卡成了突破口.html</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4795,20 +4795,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201204</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
+          <t>20201204-中国的舆论阵地要升级了</t>
         </is>
       </c>
       <c r="E133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
+          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4828,20 +4828,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20201206</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20201206-沃森生物骂战背后的斗争</t>
+          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
         </is>
       </c>
       <c r="E134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
+          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20201207</t>
+          <t>20201206</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20201207-伊朗的刺杀,印度的革命</t>
+          <t>20201206-沃森生物骂战背后的斗争</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
+          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20201208</t>
+          <t>20201207</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
+          <t>20201207-伊朗的刺杀,印度的革命</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
+          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201208</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20201209-宁波假名媛碰上了假富二代</t>
+          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
+          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20201210</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20201210-张近东把苏宁押给了马云</t>
+          <t>20201209-宁波假名媛碰上了假富二代</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
+          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20201211</t>
+          <t>20201210</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
+          <t>20201210-张近东把苏宁押给了马云</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
+          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201211</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20201212-对互联网巨头反垄断的深层理解</t>
+          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
+          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>20201213</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20201213-盲盒、卡片与多巴胺</t>
+          <t>20201212-对互联网巨头反垄断的深层理解</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
+          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20201214</t>
+          <t>20201213</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20201214-什么是'需求侧改革'</t>
+          <t>20201213-盲盒、卡片与多巴胺</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
+          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20201215</t>
+          <t>20201214</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20201215-需求侧改革与内循环</t>
+          <t>20201214-什么是'需求侧改革'</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>政事堂/20201215-需求侧改革与内循环.html</t>
+          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201215</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20201216-中芯的内斗与消费侧的机遇</t>
+          <t>20201215-需求侧改革与内循环</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
+          <t>政事堂/20201215-需求侧改革与内循环.html</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20201217</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20201217-消费侧改革释放的机会</t>
+          <t>20201216-中芯的内斗与消费侧的机遇</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
+          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20201218</t>
+          <t>20201217</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20201218-中央经济工作会议的风向标</t>
+          <t>20201217-消费侧改革释放的机会</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
+          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20201219</t>
+          <t>20201218</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20201219-互联网巨头的至暗时刻</t>
+          <t>20201218-中央经济工作会议的风向标</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
+          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201219</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
+          <t>20201219-互联网巨头的至暗时刻</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
+          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20201221</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20201221-反垄断与反混业经营</t>
+          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>政事堂/20201221-反垄断与反混业经营.html</t>
+          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20201222</t>
+          <t>20201221</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20201222-卸任前,特朗普埋了三个棋子</t>
+          <t>20201221-反垄断与反混业经营</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
+          <t>政事堂/20201221-反垄断与反混业经营.html</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20201223</t>
+          <t>20201222</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20201223-人民日报又提房地产税</t>
+          <t>20201222-卸任前,特朗普埋了三个棋子</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>政事堂/20201223-人民日报又提房地产税.html</t>
+          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20201224</t>
+          <t>20201223</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
+          <t>20201223-人民日报又提房地产税</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
+          <t>政事堂/20201223-人民日报又提房地产税.html</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201224</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20201225-英法中德美,三场胆小鬼游戏</t>
+          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
+          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>20201226</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20201226-谁是朋友,谁是敌人</t>
+          <t>20201225-英法中德美,三场胆小鬼游戏</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
+          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20201227</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20201227-反垄断之后,下一步该怎么走</t>
+          <t>20201226-谁是朋友,谁是敌人</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
+          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>20201228</t>
+          <t>20201227</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20201228-下一个二十年</t>
+          <t>20201227-反垄断之后,下一步该怎么走</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>政事堂/20201228-下一个二十年.html</t>
+          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>20201229</t>
+          <t>20201228</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20201229-涨价去库存的茅台</t>
+          <t>20201228-下一个二十年</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>政事堂/20201229-涨价去库存的茅台.html</t>
+          <t>政事堂/20201228-下一个二十年.html</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>20201230</t>
+          <t>20201229</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20201230-我们,赢了!</t>
+          <t>20201229-涨价去库存的茅台</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>政事堂/20201230-我们,赢了!.html</t>
+          <t>政事堂/20201229-涨价去库存的茅台.html</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
+          <t>20201230-我们,赢了!</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
+          <t>政事堂/20201230-我们,赢了!.html</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201230</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20201231-2020年就要过去了,我很怀念它</t>
+          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
+          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5724,15 +5724,15 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
+          <t>20201231-2020年就要过去了,我很怀念它</t>
         </is>
       </c>
       <c r="E161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
+          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5752,25 +5752,25 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
+          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
         </is>
       </c>
       <c r="E162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
+          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20210102</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20210102-山川形便与犬牙相入</t>
+          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
+          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20210103</t>
+          <t>20210102</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20210103-温莎银枪小霸王</t>
+          <t>20210102-山川形便与犬牙相入</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>政事堂/20210103-温莎银枪小霸王.html</t>
+          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20210104</t>
+          <t>20210103</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
+          <t>20210103-温莎银枪小霸王</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
+          <t>政事堂/20210103-温莎银枪小霸王.html</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20210105</t>
+          <t>20210104</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20210105-拼多多的'临时工'错在哪</t>
+          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
+          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>20210106</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20210106-民主党拿下参议院后的影响</t>
+          <t>20210105-拼多多的'临时工'错在哪</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
+          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>20210107</t>
+          <t>20210106</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20210107-国会山的陷落</t>
+          <t>20210106-民主党拿下参议院后的影响</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>政事堂/20210107-国会山的陷落.html</t>
+          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>20210108</t>
+          <t>20210107</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20210108-苹果的过去,特斯拉的未来</t>
+          <t>20210107-国会山的陷落</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
+          <t>政事堂/20210107-国会山的陷落.html</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210108</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
+          <t>20210108-苹果的过去,特斯拉的未来</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
+          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20210110-特朗普手机变'砖头'了</t>
+          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
+          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20210111</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20210111-被'杀人诛心'的特朗普</t>
+          <t>20210110-特朗普手机变'砖头'了</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
+          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>20210112</t>
+          <t>20210111</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20210112-新一轮牛市的怎么走</t>
+          <t>20210111-被'杀人诛心'的特朗普</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
+          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>20210113</t>
+          <t>20210112</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20210113-马斯克与Paypal的借道入华</t>
+          <t>20210112-新一轮牛市的怎么走</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
+          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>20210114</t>
+          <t>20210113</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20210114-一杯特殊的星巴克</t>
+          <t>20210113-马斯克与Paypal的借道入华</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
+          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20210115-中国迎来了一位女对手</t>
+          <t>20210114-一杯特殊的星巴克</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
+          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20210116</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20210116-无偿转让好,酱香来养老</t>
+          <t>20210115-中国迎来了一位女对手</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
+          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210116</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20210117-两位'小公主'的逆行之旅</t>
+          <t>20210116-无偿转让好,酱香来养老</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
+          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>20210118</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20210118-三星太子当庭被捕</t>
+          <t>20210117-两位'小公主'的逆行之旅</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>政事堂/20210118-三星太子当庭被捕.html</t>
+          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>20210119</t>
+          <t>20210118</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20210119-表演大师武契奇</t>
+          <t>20210118-三星太子当庭被捕</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>政事堂/20210119-表演大师武契奇.html</t>
+          <t>政事堂/20210118-三星太子当庭被捕.html</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>20210120</t>
+          <t>20210119</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20210120-告别特朗普</t>
+          <t>20210119-表演大师武契奇</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>政事堂/20210120-告别特朗普.html</t>
+          <t>政事堂/20210119-表演大师武契奇.html</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>20210121</t>
+          <t>20210120</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20210121-28人制裁名单,中国送别特朗普</t>
+          <t>20210120-告别特朗普</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
+          <t>政事堂/20210120-告别特朗普.html</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>20210122</t>
+          <t>20210121</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20210122-从上海飙升的房价聊起</t>
+          <t>20210121-28人制裁名单,中国送别特朗普</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
+          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210122</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20210123-走向新时代</t>
+          <t>20210122-从上海飙升的房价聊起</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>政事堂/20210123-走向新时代.html</t>
+          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>20210124</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
+          <t>20210123-走向新时代</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
+          <t>政事堂/20210123-走向新时代.html</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>20210125</t>
+          <t>20210124</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20210125-贾跃亭向左,许家印向右</t>
+          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
+          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6577,20 +6577,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20210126</t>
+          <t>20210125</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20210126-学术圈为何不能反垄断</t>
+          <t>20210125-贾跃亭向左,许家印向右</t>
         </is>
       </c>
       <c r="E187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
+          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6610,20 +6610,20 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>20210127</t>
+          <t>20210126</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20210127-废柴们如何收割华尔街大佬</t>
+          <t>20210126-学术圈为何不能反垄断</t>
         </is>
       </c>
       <c r="E188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
+          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>20210128</t>
+          <t>20210127</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20210128-资本割韭菜的套路</t>
+          <t>20210127-废柴们如何收割华尔街大佬</t>
         </is>
       </c>
       <c r="E189" t="b">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>政事堂/20210128-资本割韭菜的套路.html</t>
+          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>20210129</t>
+          <t>20210128</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20210129-从海航破产说起</t>
+          <t>20210128-资本割韭菜的套路</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>政事堂/20210129-从海航破产说起.html</t>
+          <t>政事堂/20210128-资本割韭菜的套路.html</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>20210130</t>
+          <t>20210129</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
+          <t>20210129-从海航破产说起</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
+          <t>政事堂/20210129-从海航破产说起.html</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210130</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20210131-基金要变天了......</t>
+          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>政事堂/20210131-基金要变天了.......html</t>
+          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>20210201</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20210201-缅甸政变,下一步呢</t>
+          <t>20210131-基金要变天了......</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
+          <t>政事堂/20210131-基金要变天了.......html</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -6808,20 +6808,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>20210202</t>
+          <t>20210201</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20210202-调控背后的定价权之争</t>
+          <t>20210201-缅甸政变,下一步呢</t>
         </is>
       </c>
       <c r="E194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>政事堂/20210202-调控背后的定价权之争.html</t>
+          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -6841,20 +6841,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20210203</t>
+          <t>20210202</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20210203-告别人人影视</t>
+          <t>20210202-调控背后的定价权之争</t>
         </is>
       </c>
       <c r="E195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>政事堂/20210203-告别人人影视.html</t>
+          <t>政事堂/20210202-调控背后的定价权之争.html</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>20210204</t>
+          <t>20210203</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20210204-短视频的机制</t>
+          <t>20210203-告别人人影视</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>政事堂/20210204-短视频的机制.html</t>
+          <t>政事堂/20210203-告别人人影视.html</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>20210205</t>
+          <t>20210204</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20210205-拜登的外交与A股的改革</t>
+          <t>20210204-短视频的机制</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
+          <t>政事堂/20210204-短视频的机制.html</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>20210206</t>
+          <t>20210205</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20210206-漫谈影视文化的知识产权与垄断</t>
+          <t>20210205-拜登的外交与A股的改革</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
+          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6973,20 +6973,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210206</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
+          <t>20210206-漫谈影视文化的知识产权与垄断</t>
         </is>
       </c>
       <c r="E199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
+          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7006,20 +7006,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>20210208</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20210208-知识产权秩序与短视频革命</t>
+          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
         </is>
       </c>
       <c r="E200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
+          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210208</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20210210-拼团的名媛与美国的航母</t>
+          <t>20210208-知识产权秩序与短视频革命</t>
         </is>
       </c>
       <c r="E201" t="b">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
+          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7072,20 +7072,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>20210212</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20210212-牛年的新秩序</t>
+          <t>20210210-拼团的名媛与美国的航母</t>
         </is>
       </c>
       <c r="E202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>政事堂/20210212-牛年的新秩序.html</t>
+          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>20210213</t>
+          <t>20210212</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20210213-马斯克的神化与革命</t>
+          <t>20210212-牛年的新秩序</t>
         </is>
       </c>
       <c r="E203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>政事堂/20210213-马斯克的神化与革命.html</t>
+          <t>政事堂/20210212-牛年的新秩序.html</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7138,20 +7138,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>20210215</t>
+          <t>20210213</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20210215-低生育率的原因</t>
+          <t>20210213-马斯克的神化与革命</t>
         </is>
       </c>
       <c r="E204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>政事堂/20210215-低生育率的原因.html</t>
+          <t>政事堂/20210213-马斯克的神化与革命.html</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7171,20 +7171,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>20210216</t>
+          <t>20210215</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20210216-一代版本一代神</t>
+          <t>20210215-低生育率的原因</t>
         </is>
       </c>
       <c r="E205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>政事堂/20210216-一代版本一代神.html</t>
+          <t>政事堂/20210215-低生育率的原因.html</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>20210217</t>
+          <t>20210216</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20210217-马斯克、宗教与黑客帝国</t>
+          <t>20210216-一代版本一代神</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
+          <t>政事堂/20210216-一代版本一代神.html</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210217</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20210218-品酒师入围院士,在侮辱谁</t>
+          <t>20210217-马斯克、宗教与黑客帝国</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
+          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>20210219</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
+          <t>20210218-品酒师入围院士,在侮辱谁</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
+          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7303,20 +7303,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210219</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20210221-应该用《英烈法》保护我们的英雄</t>
+          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
         </is>
       </c>
       <c r="E209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
+          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7341,15 +7341,15 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20210221-资本大佬们又要回来了</t>
+          <t>20210221-应该用《英烈法》保护我们的英雄</t>
         </is>
       </c>
       <c r="E210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
+          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>20210223</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20210223-抱团基金的走向</t>
+          <t>20210221-资本大佬们又要回来了</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>政事堂/20210223-抱团基金的走向.html</t>
+          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>20210224</t>
+          <t>20210223</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20210224-印花税打崩了抱团基金</t>
+          <t>20210223-抱团基金的走向</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
+          <t>政事堂/20210223-抱团基金的走向.html</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>20210225</t>
+          <t>20210224</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
+          <t>20210224-印花税打崩了抱团基金</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
+          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20210225-马斯克VS神,巨头的归来</t>
+          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
+          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210225</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20210226-不讲武德,拜登突袭叙利亚</t>
+          <t>20210225-马斯克VS神,巨头的归来</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
+          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>20210227</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20210227-'第一村'的华西垮不了</t>
+          <t>20210226-不讲武德,拜登突袭叙利亚</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
+          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20210228</t>
+          <t>20210227</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20210228-'大空头'巴菲特的唱空</t>
+          <t>20210227-'第一村'的华西垮不了</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
+          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210228</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20210301-凤梨与稀土</t>
+          <t>20210228-'大空头'巴菲特的唱空</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>政事堂/20210301-凤梨与稀土.html</t>
+          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -7633,12 +7633,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>20210302</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20210302-'口头加息'与'进一步加征印花税'</t>
+          <t>20210301-凤梨与稀土</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
+          <t>政事堂/20210301-凤梨与稀土.html</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7666,20 +7666,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210302</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20210303-破局：从世界工厂到世界发动机</t>
+          <t>20210302-'口头加息'与'进一步加征印花税'</t>
         </is>
       </c>
       <c r="E220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
+          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -7699,20 +7699,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>20210304</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20210304-炒币与X茅的起源</t>
+          <t>20210303-破局：从世界工厂到世界发动机</t>
         </is>
       </c>
       <c r="E221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>政事堂/20210304-炒币与X茅的起源.html</t>
+          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7732,20 +7732,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>20210305</t>
+          <t>20210304</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20210305-阳谋推恩令</t>
+          <t>20210304-炒币与X茅的起源</t>
         </is>
       </c>
       <c r="E222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>政事堂/20210305-阳谋推恩令.html</t>
+          <t>政事堂/20210304-炒币与X茅的起源.html</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7765,20 +7765,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>20210306</t>
+          <t>20210305</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20210306-拜登、白酒与新能源</t>
+          <t>20210305-阳谋推恩令</t>
         </is>
       </c>
       <c r="E223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
+          <t>政事堂/20210305-阳谋推恩令.html</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210306</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20210307-拜登、旧巨头与新神</t>
+          <t>20210306-拜登、白酒与新能源</t>
         </is>
       </c>
       <c r="E224" t="b">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
+          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>20210308</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
+          <t>20210307-拜登、旧巨头与新神</t>
         </is>
       </c>
       <c r="E225" t="b">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
+          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>20210309</t>
+          <t>20210308</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20210309-救市的国家队与撤退的集结号</t>
+          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
         </is>
       </c>
       <c r="E226" t="b">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
+          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -7897,23 +7897,89 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
+          <t>20210309</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>20210309-救市的国家队与撤退的集结号</t>
+        </is>
+      </c>
+      <c r="E227" t="b">
+        <v>1</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
           <t>20210310</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>20210310-中美的阿拉斯加会谈</t>
         </is>
       </c>
-      <c r="E227" t="b">
+      <c r="E228" t="b">
         <v>0</v>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>政事堂/20210310-中美的阿拉斯加会谈.html</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>20210311</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>20210311-中美对话新机制的建立</t>
+        </is>
+      </c>
+      <c r="E229" t="b">
+        <v>0</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>政事堂/20210311-中美对话新机制的建立.html</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
         <is>
           <t>202103</t>
         </is>

--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3140,17 +3140,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>宁南山</t>
+          <t>吃瓜群众</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20201110</t>
+          <t>20210312</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20201110-国产化,一点也不能放松</t>
+          <t>20210312-细节</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
+          <t>吃瓜群众/20210312-细节.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201110</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
+          <t>20201110-国产化,一点也不能放松</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
+          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
+          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
+          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
+          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
+          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
+          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
+          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
+          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
+          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>20201201</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
+          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
+          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201201</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
+          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
+          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
+          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
+          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20201212-巨头的使命--从一张中国地图说起</t>
+          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
+          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
+          <t>20201212-巨头的使命--从一张中国地图说起</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
+          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20201220-从两张图看成为发达国家有多难</t>
+          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
+          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
+          <t>20201220-从两张图看成为发达国家有多难</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
+          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20201231-新三线建设与年轻人的希望</t>
+          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
+          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20210101-从2021年初看未来十年的两个三条线</t>
+          <t>20201231-新三线建设与年轻人的希望</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
+          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20210109-另一个国家</t>
+          <t>20210101-从2021年初看未来十年的两个三条线</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>宁南山/20210109-另一个国家.html</t>
+          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
+          <t>20210109-另一个国家</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
+          <t>宁南山/20210109-另一个国家.html</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
+          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
+          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
+          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
+          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
+          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
+          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
+          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
+          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20210207-国产化是漫长的战役</t>
+          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>宁南山/20210207-国产化是漫长的战役.html</t>
+          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
+          <t>20210207-国产化是漫长的战役</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
+          <t>宁南山/20210207-国产化是漫长的战役.html</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20210211</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
+          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
+          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210211</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20210218-简单说下2021年预计的几件大事</t>
+          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
+          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
+          <t>20210218-简单说下2021年预计的几件大事</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
+          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
+          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
+          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
+          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
+          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
+          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
+          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20210307-从扶贫,修路到半导体</t>
+          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
+          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4130,17 +4130,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>政事堂</t>
+          <t>宁南山</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>20201114</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20201114-未来两年经济的确定性与不确定</t>
+          <t>20210307-从扶贫,修路到半导体</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
+          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20201115</t>
+          <t>20201114</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20201115-RCEP签署,为这一刻准备了30年</t>
+          <t>20201114-未来两年经济的确定性与不确定</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
+          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201115</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
+          <t>20201115-RCEP签署,为这一刻准备了30年</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
+          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>20201117</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20201117-传奇私募被传带走</t>
+          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>政事堂/20201117-传奇私募被传带走.html</t>
+          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4267,20 +4267,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201117</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20201118-莫迪终于给拜登打电话了</t>
+          <t>20201117-传奇私募被传带走</t>
         </is>
       </c>
       <c r="E117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
+          <t>政事堂/20201117-传奇私募被传带走.html</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>20201119</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20201119-谁也救不了的'蛋壳'</t>
+          <t>20201118-莫迪终于给拜登打电话了</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
+          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20201120</t>
+          <t>20201119</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20201120-坐在宝马里面笑的华晨破产了</t>
+          <t>20201119-谁也救不了的'蛋壳'</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
+          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201120</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20201121-中国考虑加入CPTPP的考量</t>
+          <t>20201120-坐在宝马里面笑的华晨破产了</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
+          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20201122</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20201122-零容忍!金融委发了尚方宝剑</t>
+          <t>20201121-中国考虑加入CPTPP的考量</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
+          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20201123</t>
+          <t>20201122</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20201123-拜登的国务卿布林肯</t>
+          <t>20201122-零容忍!金融委发了尚方宝剑</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
+          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>20201124</t>
+          <t>20201123</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20201124-东京地检调查安倍,这只是开始</t>
+          <t>20201123-拜登的国务卿布林肯</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
+          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>20201125</t>
+          <t>20201124</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
+          <t>20201124-东京地检调查安倍,这只是开始</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
+          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20201126</t>
+          <t>20201125</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20201126-投资的抉择</t>
+          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>政事堂/20201126-投资的抉择.html</t>
+          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201126</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20201127-全球即将爆发的'不讲武德'</t>
+          <t>20201126-投资的抉择</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
+          <t>政事堂/20201126-投资的抉择.html</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20201128</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
+          <t>20201127-全球即将爆发的'不讲武德'</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
+          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201128</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20201129-伊朗刺杀事件中的美国卧底</t>
+          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
+          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>20201130</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20201130-马保国凉凉之必然性分析</t>
+          <t>20201129-伊朗刺杀事件中的美国卧底</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
+          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4696,25 +4696,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20201202</t>
+          <t>20201130</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20201202-为何要持续去怼澳大利亚</t>
+          <t>20201130-马保国凉凉之必然性分析</t>
         </is>
       </c>
       <c r="E130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
+          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20201202-关于胡锡进的一则短评</t>
+          <t>20201202-为何要持续去怼澳大利亚</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
+          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>20201203</t>
+          <t>20201202</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20201203-伊万卡成了突破口</t>
+          <t>20201202-关于胡锡进的一则短评</t>
         </is>
       </c>
       <c r="E132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>政事堂/20201203-伊万卡成了突破口.html</t>
+          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20201204</t>
+          <t>20201203</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20201204-中国的舆论阵地要升级了</t>
+          <t>20201203-伊万卡成了突破口</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
+          <t>政事堂/20201203-伊万卡成了突破口.html</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4828,20 +4828,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201204</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
+          <t>20201204-中国的舆论阵地要升级了</t>
         </is>
       </c>
       <c r="E134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
+          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4861,20 +4861,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20201206</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20201206-沃森生物骂战背后的斗争</t>
+          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
         </is>
       </c>
       <c r="E135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
+          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20201207</t>
+          <t>20201206</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20201207-伊朗的刺杀,印度的革命</t>
+          <t>20201206-沃森生物骂战背后的斗争</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
+          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20201208</t>
+          <t>20201207</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
+          <t>20201207-伊朗的刺杀,印度的革命</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
+          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201208</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20201209-宁波假名媛碰上了假富二代</t>
+          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
+          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20201210</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20201210-张近东把苏宁押给了马云</t>
+          <t>20201209-宁波假名媛碰上了假富二代</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
+          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20201211</t>
+          <t>20201210</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
+          <t>20201210-张近东把苏宁押给了马云</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
+          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201211</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20201212-对互联网巨头反垄断的深层理解</t>
+          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
+          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20201213</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20201213-盲盒、卡片与多巴胺</t>
+          <t>20201212-对互联网巨头反垄断的深层理解</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
+          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20201214</t>
+          <t>20201213</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20201214-什么是'需求侧改革'</t>
+          <t>20201213-盲盒、卡片与多巴胺</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
+          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20201215</t>
+          <t>20201214</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20201215-需求侧改革与内循环</t>
+          <t>20201214-什么是'需求侧改革'</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>政事堂/20201215-需求侧改革与内循环.html</t>
+          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201215</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20201216-中芯的内斗与消费侧的机遇</t>
+          <t>20201215-需求侧改革与内循环</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
+          <t>政事堂/20201215-需求侧改革与内循环.html</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20201217</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20201217-消费侧改革释放的机会</t>
+          <t>20201216-中芯的内斗与消费侧的机遇</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
+          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20201218</t>
+          <t>20201217</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20201218-中央经济工作会议的风向标</t>
+          <t>20201217-消费侧改革释放的机会</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
+          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20201219</t>
+          <t>20201218</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20201219-互联网巨头的至暗时刻</t>
+          <t>20201218-中央经济工作会议的风向标</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
+          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201219</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
+          <t>20201219-互联网巨头的至暗时刻</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
+          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20201221</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20201221-反垄断与反混业经营</t>
+          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>政事堂/20201221-反垄断与反混业经营.html</t>
+          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20201222</t>
+          <t>20201221</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20201222-卸任前,特朗普埋了三个棋子</t>
+          <t>20201221-反垄断与反混业经营</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
+          <t>政事堂/20201221-反垄断与反混业经营.html</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20201223</t>
+          <t>20201222</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20201223-人民日报又提房地产税</t>
+          <t>20201222-卸任前,特朗普埋了三个棋子</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>政事堂/20201223-人民日报又提房地产税.html</t>
+          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20201224</t>
+          <t>20201223</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
+          <t>20201223-人民日报又提房地产税</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
+          <t>政事堂/20201223-人民日报又提房地产税.html</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201224</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20201225-英法中德美,三场胆小鬼游戏</t>
+          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
+          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20201226</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20201226-谁是朋友,谁是敌人</t>
+          <t>20201225-英法中德美,三场胆小鬼游戏</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
+          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>20201227</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20201227-反垄断之后,下一步该怎么走</t>
+          <t>20201226-谁是朋友,谁是敌人</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
+          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>20201228</t>
+          <t>20201227</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20201228-下一个二十年</t>
+          <t>20201227-反垄断之后,下一步该怎么走</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>政事堂/20201228-下一个二十年.html</t>
+          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>20201229</t>
+          <t>20201228</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20201229-涨价去库存的茅台</t>
+          <t>20201228-下一个二十年</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>政事堂/20201229-涨价去库存的茅台.html</t>
+          <t>政事堂/20201228-下一个二十年.html</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>20201230</t>
+          <t>20201229</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20201230-我们,赢了!</t>
+          <t>20201229-涨价去库存的茅台</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>政事堂/20201230-我们,赢了!.html</t>
+          <t>政事堂/20201229-涨价去库存的茅台.html</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
+          <t>20201230-我们,赢了!</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
+          <t>政事堂/20201230-我们,赢了!.html</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201230</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20201231-2020年就要过去了,我很怀念它</t>
+          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
+          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5757,15 +5757,15 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
+          <t>20201231-2020年就要过去了,我很怀念它</t>
         </is>
       </c>
       <c r="E162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
+          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5785,25 +5785,25 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
+          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
+          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20210102</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20210102-山川形便与犬牙相入</t>
+          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
+          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20210103</t>
+          <t>20210102</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20210103-温莎银枪小霸王</t>
+          <t>20210102-山川形便与犬牙相入</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>政事堂/20210103-温莎银枪小霸王.html</t>
+          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20210104</t>
+          <t>20210103</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
+          <t>20210103-温莎银枪小霸王</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
+          <t>政事堂/20210103-温莎银枪小霸王.html</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>20210105</t>
+          <t>20210104</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20210105-拼多多的'临时工'错在哪</t>
+          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
+          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>20210106</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20210106-民主党拿下参议院后的影响</t>
+          <t>20210105-拼多多的'临时工'错在哪</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
+          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>20210107</t>
+          <t>20210106</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20210107-国会山的陷落</t>
+          <t>20210106-民主党拿下参议院后的影响</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>政事堂/20210107-国会山的陷落.html</t>
+          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>20210108</t>
+          <t>20210107</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20210108-苹果的过去,特斯拉的未来</t>
+          <t>20210107-国会山的陷落</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
+          <t>政事堂/20210107-国会山的陷落.html</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210108</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
+          <t>20210108-苹果的过去,特斯拉的未来</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
+          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20210110-特朗普手机变'砖头'了</t>
+          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
+          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>20210111</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20210111-被'杀人诛心'的特朗普</t>
+          <t>20210110-特朗普手机变'砖头'了</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
+          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>20210112</t>
+          <t>20210111</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20210112-新一轮牛市的怎么走</t>
+          <t>20210111-被'杀人诛心'的特朗普</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
+          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>20210113</t>
+          <t>20210112</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20210113-马斯克与Paypal的借道入华</t>
+          <t>20210112-新一轮牛市的怎么走</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
+          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>20210114</t>
+          <t>20210113</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20210114-一杯特殊的星巴克</t>
+          <t>20210113-马斯克与Paypal的借道入华</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
+          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20210115-中国迎来了一位女对手</t>
+          <t>20210114-一杯特殊的星巴克</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
+          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>20210116</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20210116-无偿转让好,酱香来养老</t>
+          <t>20210115-中国迎来了一位女对手</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
+          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210116</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20210117-两位'小公主'的逆行之旅</t>
+          <t>20210116-无偿转让好,酱香来养老</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
+          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>20210118</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20210118-三星太子当庭被捕</t>
+          <t>20210117-两位'小公主'的逆行之旅</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>政事堂/20210118-三星太子当庭被捕.html</t>
+          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>20210119</t>
+          <t>20210118</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20210119-表演大师武契奇</t>
+          <t>20210118-三星太子当庭被捕</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>政事堂/20210119-表演大师武契奇.html</t>
+          <t>政事堂/20210118-三星太子当庭被捕.html</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>20210120</t>
+          <t>20210119</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20210120-告别特朗普</t>
+          <t>20210119-表演大师武契奇</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>政事堂/20210120-告别特朗普.html</t>
+          <t>政事堂/20210119-表演大师武契奇.html</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>20210121</t>
+          <t>20210120</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20210121-28人制裁名单,中国送别特朗普</t>
+          <t>20210120-告别特朗普</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
+          <t>政事堂/20210120-告别特朗普.html</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>20210122</t>
+          <t>20210121</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20210122-从上海飙升的房价聊起</t>
+          <t>20210121-28人制裁名单,中国送别特朗普</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
+          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210122</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20210123-走向新时代</t>
+          <t>20210122-从上海飙升的房价聊起</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>政事堂/20210123-走向新时代.html</t>
+          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>20210124</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
+          <t>20210123-走向新时代</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
+          <t>政事堂/20210123-走向新时代.html</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20210125</t>
+          <t>20210124</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20210125-贾跃亭向左,许家印向右</t>
+          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
+          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6610,20 +6610,20 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>20210126</t>
+          <t>20210125</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20210126-学术圈为何不能反垄断</t>
+          <t>20210125-贾跃亭向左,许家印向右</t>
         </is>
       </c>
       <c r="E188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
+          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6643,20 +6643,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>20210127</t>
+          <t>20210126</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20210127-废柴们如何收割华尔街大佬</t>
+          <t>20210126-学术圈为何不能反垄断</t>
         </is>
       </c>
       <c r="E189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
+          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>20210128</t>
+          <t>20210127</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20210128-资本割韭菜的套路</t>
+          <t>20210127-废柴们如何收割华尔街大佬</t>
         </is>
       </c>
       <c r="E190" t="b">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>政事堂/20210128-资本割韭菜的套路.html</t>
+          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>20210129</t>
+          <t>20210128</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20210129-从海航破产说起</t>
+          <t>20210128-资本割韭菜的套路</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>政事堂/20210129-从海航破产说起.html</t>
+          <t>政事堂/20210128-资本割韭菜的套路.html</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>20210130</t>
+          <t>20210129</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
+          <t>20210129-从海航破产说起</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
+          <t>政事堂/20210129-从海航破产说起.html</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210130</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20210131-基金要变天了......</t>
+          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>政事堂/20210131-基金要变天了.......html</t>
+          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>20210201</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20210201-缅甸政变,下一步呢</t>
+          <t>20210131-基金要变天了......</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
+          <t>政事堂/20210131-基金要变天了.......html</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -6841,20 +6841,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20210202</t>
+          <t>20210201</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20210202-调控背后的定价权之争</t>
+          <t>20210201-缅甸政变,下一步呢</t>
         </is>
       </c>
       <c r="E195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>政事堂/20210202-调控背后的定价权之争.html</t>
+          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -6874,20 +6874,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>20210203</t>
+          <t>20210202</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20210203-告别人人影视</t>
+          <t>20210202-调控背后的定价权之争</t>
         </is>
       </c>
       <c r="E196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>政事堂/20210203-告别人人影视.html</t>
+          <t>政事堂/20210202-调控背后的定价权之争.html</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>20210204</t>
+          <t>20210203</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20210204-短视频的机制</t>
+          <t>20210203-告别人人影视</t>
         </is>
       </c>
       <c r="E197" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>政事堂/20210204-短视频的机制.html</t>
+          <t>政事堂/20210203-告别人人影视.html</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>20210205</t>
+          <t>20210204</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20210205-拜登的外交与A股的改革</t>
+          <t>20210204-短视频的机制</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
+          <t>政事堂/20210204-短视频的机制.html</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>20210206</t>
+          <t>20210205</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20210206-漫谈影视文化的知识产权与垄断</t>
+          <t>20210205-拜登的外交与A股的改革</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
+          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7006,20 +7006,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210206</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
+          <t>20210206-漫谈影视文化的知识产权与垄断</t>
         </is>
       </c>
       <c r="E200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
+          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7039,20 +7039,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>20210208</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20210208-知识产权秩序与短视频革命</t>
+          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
         </is>
       </c>
       <c r="E201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
+          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210208</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20210210-拼团的名媛与美国的航母</t>
+          <t>20210208-知识产权秩序与短视频革命</t>
         </is>
       </c>
       <c r="E202" t="b">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
+          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7105,20 +7105,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>20210212</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20210212-牛年的新秩序</t>
+          <t>20210210-拼团的名媛与美国的航母</t>
         </is>
       </c>
       <c r="E203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>政事堂/20210212-牛年的新秩序.html</t>
+          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7138,20 +7138,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>20210213</t>
+          <t>20210212</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20210213-马斯克的神化与革命</t>
+          <t>20210212-牛年的新秩序</t>
         </is>
       </c>
       <c r="E204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>政事堂/20210213-马斯克的神化与革命.html</t>
+          <t>政事堂/20210212-牛年的新秩序.html</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7171,20 +7171,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>20210215</t>
+          <t>20210213</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20210215-低生育率的原因</t>
+          <t>20210213-马斯克的神化与革命</t>
         </is>
       </c>
       <c r="E205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>政事堂/20210215-低生育率的原因.html</t>
+          <t>政事堂/20210213-马斯克的神化与革命.html</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7204,20 +7204,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>20210216</t>
+          <t>20210215</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20210216-一代版本一代神</t>
+          <t>20210215-低生育率的原因</t>
         </is>
       </c>
       <c r="E206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>政事堂/20210216-一代版本一代神.html</t>
+          <t>政事堂/20210215-低生育率的原因.html</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>20210217</t>
+          <t>20210216</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20210217-马斯克、宗教与黑客帝国</t>
+          <t>20210216-一代版本一代神</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
+          <t>政事堂/20210216-一代版本一代神.html</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210217</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20210218-品酒师入围院士,在侮辱谁</t>
+          <t>20210217-马斯克、宗教与黑客帝国</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
+          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>20210219</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
+          <t>20210218-品酒师入围院士,在侮辱谁</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
+          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7336,20 +7336,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210219</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20210221-应该用《英烈法》保护我们的英雄</t>
+          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
         </is>
       </c>
       <c r="E210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
+          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7374,15 +7374,15 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20210221-资本大佬们又要回来了</t>
+          <t>20210221-应该用《英烈法》保护我们的英雄</t>
         </is>
       </c>
       <c r="E211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
+          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>20210223</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20210223-抱团基金的走向</t>
+          <t>20210221-资本大佬们又要回来了</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>政事堂/20210223-抱团基金的走向.html</t>
+          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>20210224</t>
+          <t>20210223</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20210224-印花税打崩了抱团基金</t>
+          <t>20210223-抱团基金的走向</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
+          <t>政事堂/20210223-抱团基金的走向.html</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>20210225</t>
+          <t>20210224</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
+          <t>20210224-印花税打崩了抱团基金</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
+          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20210225-马斯克VS神,巨头的归来</t>
+          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
+          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210225</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20210226-不讲武德,拜登突袭叙利亚</t>
+          <t>20210225-马斯克VS神,巨头的归来</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
+          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20210227</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20210227-'第一村'的华西垮不了</t>
+          <t>20210226-不讲武德,拜登突袭叙利亚</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
+          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>20210228</t>
+          <t>20210227</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20210228-'大空头'巴菲特的唱空</t>
+          <t>20210227-'第一村'的华西垮不了</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
+          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210228</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20210301-凤梨与稀土</t>
+          <t>20210228-'大空头'巴菲特的唱空</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>政事堂/20210301-凤梨与稀土.html</t>
+          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>20210302</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20210302-'口头加息'与'进一步加征印花税'</t>
+          <t>20210301-凤梨与稀土</t>
         </is>
       </c>
       <c r="E220" t="b">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
+          <t>政事堂/20210301-凤梨与稀土.html</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -7699,20 +7699,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210302</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20210303-破局：从世界工厂到世界发动机</t>
+          <t>20210302-'口头加息'与'进一步加征印花税'</t>
         </is>
       </c>
       <c r="E221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
+          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7732,20 +7732,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>20210304</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20210304-炒币与X茅的起源</t>
+          <t>20210303-破局：从世界工厂到世界发动机</t>
         </is>
       </c>
       <c r="E222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>政事堂/20210304-炒币与X茅的起源.html</t>
+          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7765,20 +7765,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>20210305</t>
+          <t>20210304</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20210305-阳谋推恩令</t>
+          <t>20210304-炒币与X茅的起源</t>
         </is>
       </c>
       <c r="E223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>政事堂/20210305-阳谋推恩令.html</t>
+          <t>政事堂/20210304-炒币与X茅的起源.html</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -7798,20 +7798,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>20210306</t>
+          <t>20210305</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20210306-拜登、白酒与新能源</t>
+          <t>20210305-阳谋推恩令</t>
         </is>
       </c>
       <c r="E224" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
+          <t>政事堂/20210305-阳谋推恩令.html</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210306</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20210307-拜登、旧巨头与新神</t>
+          <t>20210306-拜登、白酒与新能源</t>
         </is>
       </c>
       <c r="E225" t="b">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
+          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>20210308</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
+          <t>20210307-拜登、旧巨头与新神</t>
         </is>
       </c>
       <c r="E226" t="b">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
+          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>20210309</t>
+          <t>20210308</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20210309-救市的国家队与撤退的集结号</t>
+          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
         </is>
       </c>
       <c r="E227" t="b">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
+          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -7930,20 +7930,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>20210310</t>
+          <t>20210309</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20210310-中美的阿拉斯加会谈</t>
+          <t>20210309-救市的国家队与撤退的集结号</t>
         </is>
       </c>
       <c r="E228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>政事堂/20210310-中美的阿拉斯加会谈.html</t>
+          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -7963,23 +7963,89 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
+          <t>20210310</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>20210310-中美的阿拉斯加会谈</t>
+        </is>
+      </c>
+      <c r="E229" t="b">
+        <v>1</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>政事堂/20210310-中美的阿拉斯加会谈.html</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
           <t>20210311</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>20210311-中美对话新机制的建立</t>
         </is>
       </c>
-      <c r="E229" t="b">
+      <c r="E230" t="b">
+        <v>1</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>政事堂/20210311-中美对话新机制的建立.html</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>20210312</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>20210312-整顿校外培训,'减负'为了谁</t>
+        </is>
+      </c>
+      <c r="E231" t="b">
         <v>0</v>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>政事堂/20210311-中美对话新机制的建立.html</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>政事堂/20210312-整顿校外培训,'减负'为了谁.html</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
         <is>
           <t>202103</t>
         </is>

--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20201113-特朗普真的要发动热战,谋求连任</t>
+          <t>特朗普真的要发动热战,谋求连任</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -485,7 +485,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201113-特朗普真的要发动热战,谋求连任.html</t>
+          <t>吃瓜群众/2020/11/13-特朗普真的要发动热战,谋求连任.html</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20201114-真的能从公开信息,看清世界真相吗</t>
+          <t>真的能从公开信息,看清世界真相吗</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -518,7 +518,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201114-真的能从公开信息,看清世界真相吗.html</t>
+          <t>吃瓜群众/2020/11/14-真的能从公开信息,看清世界真相吗.html</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20201115-今天,RCEP正式签订!!</t>
+          <t>今天,RCEP正式签订!!</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -551,7 +551,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201115-今天,RCEP正式签订!!.html</t>
+          <t>吃瓜群众/2020/11/15-今天,RCEP正式签订!!.html</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20201116-特朗普到底是奸商窃国,还是天降伟人</t>
+          <t>特朗普到底是奸商窃国,还是天降伟人</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -584,7 +584,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201116-特朗普到底是奸商窃国,还是天降伟人.html</t>
+          <t>吃瓜群众/2020/11/16-特朗普到底是奸商窃国,还是天降伟人.html</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20201117-迷失在历史进程中的马云们……</t>
+          <t>迷失在历史进程中的马云们……</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -617,7 +617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201117-迷失在历史进程中的马云们…….html</t>
+          <t>吃瓜群众/2020/11/17-迷失在历史进程中的马云们…….html</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20201118-有文化的人,是怎样追女孩子的</t>
+          <t>有文化的人,是怎样追女孩子的</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -650,7 +650,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201118-有文化的人,是怎样追女孩子的.html</t>
+          <t>吃瓜群众/2020/11/18-有文化的人,是怎样追女孩子的.html</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20201119-美国军方,把特朗普给卖了</t>
+          <t>美国军方,把特朗普给卖了</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -683,7 +683,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201119-美国军方,把特朗普给卖了.html</t>
+          <t>吃瓜群众/2020/11/19-美国军方,把特朗普给卖了.html</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20201120-历史的进程</t>
+          <t>历史的进程</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -716,7 +716,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201120-历史的进程.html</t>
+          <t>吃瓜群众/2020/11/20-历史的进程.html</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20201120-清北硕博去杭州街道办,又是一盘大棋</t>
+          <t>清北硕博去杭州街道办,又是一盘大棋</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -749,7 +749,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201120-清北硕博去杭州街道办,又是一盘大棋.html</t>
+          <t>吃瓜群众/2020/11/20-清北硕博去杭州街道办,又是一盘大棋.html</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20201120-金融副省长们</t>
+          <t>金融副省长们</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -782,7 +782,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201120-金融副省长们.html</t>
+          <t>吃瓜群众/2020/11/20-金融副省长们.html</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20201120-青年们的往事</t>
+          <t>青年们的往事</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -815,7 +815,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201120-青年们的往事.html</t>
+          <t>吃瓜群众/2020/11/20-青年们的往事.html</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20201121-人事这门学问,最高级的就是摸清历史发展的脉络</t>
+          <t>人事这门学问,最高级的就是摸清历史发展的脉络</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -848,7 +848,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201121-人事这门学问,最高级的就是摸清历史发展的脉络.html</t>
+          <t>吃瓜群众/2020/11/21-人事这门学问,最高级的就是摸清历史发展的脉络.html</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20201122-教你面相和中医</t>
+          <t>教你面相和中医</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201122-教你面相和中医.html</t>
+          <t>吃瓜群众/2020/11/22-教你面相和中医.html</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20201123-华晨的政商往事</t>
+          <t>华晨的政商往事</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201123-华晨的政商往事.html</t>
+          <t>吃瓜群众/2020/11/23-华晨的政商往事.html</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20201124-美国大麻要合法化了,中国会放开毒品吗</t>
+          <t>美国大麻要合法化了,中国会放开毒品吗</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -947,7 +947,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201124-美国大麻要合法化了,中国会放开毒品吗.html</t>
+          <t>吃瓜群众/2020/11/24-美国大麻要合法化了,中国会放开毒品吗.html</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20201125-人类两次民族大融合(上)</t>
+          <t>人类两次民族大融合(上)</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -980,7 +980,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201125-人类两次民族大融合(上).html</t>
+          <t>吃瓜群众/2020/11/25-人类两次民族大融合(上).html</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20201126-特朗普,要被联合绞杀了-微博</t>
+          <t>特朗普,要被联合绞杀了-微博</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201126-特朗普,要被联合绞杀了-微博.html</t>
+          <t>吃瓜群众/2020/11/26-特朗普,要被联合绞杀了-微博.html</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20201126-特朗普,要被联合绞杀了</t>
+          <t>特朗普,要被联合绞杀了</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201126-特朗普,要被联合绞杀了.html</t>
+          <t>吃瓜群众/2020/11/26-特朗普,要被联合绞杀了.html</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20201127-岱岱洗稿</t>
+          <t>岱岱洗稿</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201127-岱岱洗稿.html</t>
+          <t>吃瓜群众/2020/11/27-岱岱洗稿.html</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20201129-基辛格被特朗普炒鱿鱼了,回顾下基辛格的名言</t>
+          <t>基辛格被特朗普炒鱿鱼了,回顾下基辛格的名言</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201129-基辛格被特朗普炒鱿鱼了,回顾下基辛格的名言.html</t>
+          <t>吃瓜群众/2020/11/29-基辛格被特朗普炒鱿鱼了,回顾下基辛格的名言.html</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20201130-澳大利亚给拜登重返亚太当急先锋,结果被中国直接摁死!</t>
+          <t>澳大利亚给拜登重返亚太当急先锋,结果被中国直接摁死!</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201130-澳大利亚给拜登重返亚太当急先锋,结果被中国直接摁死!.html</t>
+          <t>吃瓜群众/2020/11/30-澳大利亚给拜登重返亚太当急先锋,结果被中国直接摁死!.html</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20201201-被屡屡挑衅的伊朗,会不会和以色列开战呢</t>
+          <t>被屡屡挑衅的伊朗,会不会和以色列开战呢</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201201-被屡屡挑衅的伊朗,会不会和以色列开战呢.html</t>
+          <t>吃瓜群众/2020/12/01-被屡屡挑衅的伊朗,会不会和以色列开战呢.html</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20201202-胡锡进有私生子扯淡!就是公知们故意搞他!</t>
+          <t>胡锡进有私生子扯淡!就是公知们故意搞他!</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201202-胡锡进有私生子扯淡!就是公知们故意搞他!.html</t>
+          <t>吃瓜群众/2020/12/02-胡锡进有私生子扯淡!就是公知们故意搞他!.html</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20201203-普京和蓬佩奥,将死亡边缘的特朗普拉了回来</t>
+          <t>普京和蓬佩奥,将死亡边缘的特朗普拉了回来</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201203-普京和蓬佩奥,将死亡边缘的特朗普拉了回来.html</t>
+          <t>吃瓜群众/2020/12/03-普京和蓬佩奥,将死亡边缘的特朗普拉了回来.html</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20201204-美国阉党-蓬佩奥的86届西点帮</t>
+          <t>美国阉党-蓬佩奥的86届西点帮</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201204-美国阉党-蓬佩奥的86届西点帮.html</t>
+          <t>吃瓜群众/2020/12/04-美国阉党-蓬佩奥的86届西点帮.html</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20201205-蛋壳爆雷,寒了人心</t>
+          <t>蛋壳爆雷,寒了人心</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201205-蛋壳爆雷,寒了人心.html</t>
+          <t>吃瓜群众/2020/12/05-蛋壳爆雷,寒了人心.html</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20201206-迷失在历史进程中的互联网资本们……</t>
+          <t>迷失在历史进程中的互联网资本们……</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201206-迷失在历史进程中的互联网资本们…….html</t>
+          <t>吃瓜群众/2020/12/06-迷失在历史进程中的互联网资本们…….html</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20201207-伊朗复仇刺杀以色列高官你信你就上当了!这是假新闻!</t>
+          <t>伊朗复仇刺杀以色列高官你信你就上当了!这是假新闻!</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201207-伊朗复仇刺杀以色列高官你信你就上当了!这是假新闻!.html</t>
+          <t>吃瓜群众/2020/12/07-伊朗复仇刺杀以色列高官你信你就上当了!这是假新闻!.html</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20201208-从公开新闻,看透这个世界的真相</t>
+          <t>从公开新闻,看透这个世界的真相</t>
         </is>
       </c>
       <c r="E30" t="b">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201208-从公开新闻,看透这个世界的真相.html</t>
+          <t>吃瓜群众/2020/12/08-从公开新闻,看透这个世界的真相.html</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20201209-中国人民的老朋友——布什家族</t>
+          <t>中国人民的老朋友——布什家族</t>
         </is>
       </c>
       <c r="E31" t="b">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201209-中国人民的老朋友——布什家族.html</t>
+          <t>吃瓜群众/2020/12/09-中国人民的老朋友——布什家族.html</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20201210-趣谈中国各省</t>
+          <t>趣谈中国各省</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201210-趣谈中国各省.html</t>
+          <t>吃瓜群众/2020/12/10-趣谈中国各省.html</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20201211-'投资不过南宋版图',怎么解决南北差距问题</t>
+          <t>'投资不过南宋版图',怎么解决南北差距问题</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201211-'投资不过南宋版图',怎么解决南北差距问题.html</t>
+          <t>吃瓜群众/2020/12/11-'投资不过南宋版图',怎么解决南北差距问题.html</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20201212-中美摔杯为号,要一起对互联网巨头动手了</t>
+          <t>中美摔杯为号,要一起对互联网巨头动手了</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201212-中美摔杯为号,要一起对互联网巨头动手了.html</t>
+          <t>吃瓜群众/2020/12/12-中美摔杯为号,要一起对互联网巨头动手了.html</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20201213-被美国人民抛弃的扎克伯格</t>
+          <t>被美国人民抛弃的扎克伯格</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201213-被美国人民抛弃的扎克伯格.html</t>
+          <t>吃瓜群众/2020/12/13-被美国人民抛弃的扎克伯格.html</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20201214-睁眼看世界丨一篇讲透互联网的神文</t>
+          <t>睁眼看世界丨一篇讲透互联网的神文</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201214-睁眼看世界丨一篇讲透互联网的神文.html</t>
+          <t>吃瓜群众/2020/12/14-睁眼看世界丨一篇讲透互联网的神文.html</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20201215-[番外]互联网是人类历史的一段弯路吗</t>
+          <t>[番外]互联网是人类历史的一段弯路吗</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201215-[番外]互联网是人类历史的一段弯路吗.html</t>
+          <t>吃瓜群众/2020/12/15-[番外]互联网是人类历史的一段弯路吗.html</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20201215-普京祝贺拜登!特朗普要被世界抛弃吗</t>
+          <t>普京祝贺拜登!特朗普要被世界抛弃吗</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201215-普京祝贺拜登!特朗普要被世界抛弃吗.html</t>
+          <t>吃瓜群众/2020/12/15-普京祝贺拜登!特朗普要被世界抛弃吗.html</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20201217-犹太人为什么牛逼因为踩中了四次历史进程</t>
+          <t>犹太人为什么牛逼因为踩中了四次历史进程</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201217-犹太人为什么牛逼因为踩中了四次历史进程.html</t>
+          <t>吃瓜群众/2020/12/17-犹太人为什么牛逼因为踩中了四次历史进程.html</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20201218-比特币大涨背后的可能性分析</t>
+          <t>比特币大涨背后的可能性分析</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201218-比特币大涨背后的可能性分析.html</t>
+          <t>吃瓜群众/2020/12/18-比特币大涨背后的可能性分析.html</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20201219-成绩很辉煌,我们很清醒——经济工作会议解读</t>
+          <t>成绩很辉煌,我们很清醒——经济工作会议解读</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201219-成绩很辉煌,我们很清醒——经济工作会议解读.html</t>
+          <t>吃瓜群众/2020/12/19-成绩很辉煌,我们很清醒——经济工作会议解读.html</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20201220-国家为什么要反对垄断资本和金融资本</t>
+          <t>国家为什么要反对垄断资本和金融资本</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201220-国家为什么要反对垄断资本和金融资本.html</t>
+          <t>吃瓜群众/2020/12/20-国家为什么要反对垄断资本和金融资本.html</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20201221-中国为内循环,早已准备了几十年</t>
+          <t>中国为内循环,早已准备了几十年</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201221-中国为内循环,早已准备了几十年.html</t>
+          <t>吃瓜群众/2020/12/21-中国为内循环,早已准备了几十年.html</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20201222-中央经济工作会议,结束了吗</t>
+          <t>中央经济工作会议,结束了吗</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201222-中央经济工作会议,结束了吗.html</t>
+          <t>吃瓜群众/2020/12/22-中央经济工作会议,结束了吗.html</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20201224-一篇随笔丨马云的国际朋友,不管用了</t>
+          <t>一篇随笔丨马云的国际朋友,不管用了</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201224-一篇随笔丨马云的国际朋友,不管用了.html</t>
+          <t>吃瓜群众/2020/12/24-一篇随笔丨马云的国际朋友,不管用了.html</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20201226-在2020年,更想毛泽东</t>
+          <t>在2020年,更想毛泽东</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201226-在2020年,更想毛泽东.html</t>
+          <t>吃瓜群众/2020/12/26-在2020年,更想毛泽东.html</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20201228-年末了,大家注意防疫</t>
+          <t>年末了,大家注意防疫</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201228-年末了,大家注意防疫.html</t>
+          <t>吃瓜群众/2020/12/28-年末了,大家注意防疫.html</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20201229-谈小镇做题家</t>
+          <t>谈小镇做题家</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201229-谈小镇做题家.html</t>
+          <t>吃瓜群众/2020/12/29-谈小镇做题家.html</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20201230-中欧协议,定了!</t>
+          <t>中欧协议,定了!</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201230-中欧协议,定了!.html</t>
+          <t>吃瓜群众/2020/12/30-中欧协议,定了!.html</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20201231-进来,和岱岱说说话</t>
+          <t>进来,和岱岱说说话</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>吃瓜群众/20201231-进来,和岱岱说说话.html</t>
+          <t>吃瓜群众/2020/12/31-进来,和岱岱说说话.html</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20210101-关注微博,元旦快乐</t>
+          <t>关注微博,元旦快乐</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210101-关注微博,元旦快乐.html</t>
+          <t>吃瓜群众/2021/01/01-关注微博,元旦快乐.html</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20210105-人类文明最伟大的两次凝视</t>
+          <t>人类文明最伟大的两次凝视</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210105-人类文明最伟大的两次凝视.html</t>
+          <t>吃瓜群众/2021/01/05-人类文明最伟大的两次凝视.html</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20210106-一叶知秋看新闻</t>
+          <t>一叶知秋看新闻</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210106-一叶知秋看新闻.html</t>
+          <t>吃瓜群众/2021/01/06-一叶知秋看新闻.html</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20210107-美国,气数已尽</t>
+          <t>美国,气数已尽</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210107-美国,气数已尽.html</t>
+          <t>吃瓜群众/2021/01/07-美国,气数已尽.html</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20210109-美国提前清算特朗普,中国喜提最美剧本!</t>
+          <t>美国提前清算特朗普,中国喜提最美剧本!</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210109-美国提前清算特朗普,中国喜提最美剧本!.html</t>
+          <t>吃瓜群众/2021/01/09-美国提前清算特朗普,中国喜提最美剧本!.html</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20210110-卧看千山急雨来</t>
+          <t>卧看千山急雨来</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210110-卧看千山急雨来.html</t>
+          <t>吃瓜群众/2021/01/10-卧看千山急雨来.html</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20210111-有错就要认,挨打要立正</t>
+          <t>有错就要认,挨打要立正</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210111-有错就要认,挨打要立正.html</t>
+          <t>吃瓜群众/2021/01/11-有错就要认,挨打要立正.html</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20210112-未来十天,复兴一跃!</t>
+          <t>未来十天,复兴一跃!</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210112-未来十天,复兴一跃!.html</t>
+          <t>吃瓜群众/2021/01/12-未来十天,复兴一跃!.html</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20210113-中国喊出未来十天是台海窗口期,美国'怂'了吗</t>
+          <t>中国喊出未来十天是台海窗口期,美国'怂'了吗</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210113-中国喊出未来十天是台海窗口期,美国'怂'了吗.html</t>
+          <t>吃瓜群众/2021/01/13-中国喊出未来十天是台海窗口期,美国'怂'了吗.html</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20210114-愿我有生之日,得见你君临天下</t>
+          <t>愿我有生之日,得见你君临天下</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210114-愿我有生之日,得见你君临天下.html</t>
+          <t>吃瓜群众/2021/01/14-愿我有生之日,得见你君临天下.html</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20210115-愿我有生之日,得见你君临天下</t>
+          <t>愿我有生之日,得见你君临天下</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210115-愿我有生之日,得见你君临天下.html</t>
+          <t>吃瓜群众/2021/01/15-愿我有生之日,得见你君临天下.html</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20210116-以什么理由,来梧桐花开呢</t>
+          <t>以什么理由,来梧桐花开呢</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210116-以什么理由,来梧桐花开呢.html</t>
+          <t>吃瓜群众/2021/01/16-以什么理由,来梧桐花开呢.html</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20210124-陌上花开否缓缓归来矣</t>
+          <t>陌上花开否缓缓归来矣</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210124-陌上花开否缓缓归来矣.html</t>
+          <t>吃瓜群众/2021/01/24-陌上花开否缓缓归来矣.html</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20210125-拜登一上台,俄罗斯就乱了</t>
+          <t>拜登一上台,俄罗斯就乱了</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210125-拜登一上台,俄罗斯就乱了.html</t>
+          <t>吃瓜群众/2021/01/25-拜登一上台,俄罗斯就乱了.html</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20210126-通化抗疫丨领导无能,累死基层</t>
+          <t>通化抗疫丨领导无能,累死基层</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210126-通化抗疫丨领导无能,累死基层.html</t>
+          <t>吃瓜群众/2021/01/26-通化抗疫丨领导无能,累死基层.html</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20210127-笔杆子丨国内各大新闻媒体大起底</t>
+          <t>笔杆子丨国内各大新闻媒体大起底</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210127-笔杆子丨国内各大新闻媒体大起底.html</t>
+          <t>吃瓜群众/2021/01/27-笔杆子丨国内各大新闻媒体大起底.html</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20210128-辽宁舰的背后丨'这是中华民族唯一的机会,如果错过,我自己都不会原谅自己!'</t>
+          <t>辽宁舰的背后丨'这是中华民族唯一的机会,如果错过,我自己都不会原谅自己!'</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210128-辽宁舰的背后丨'这是中华民族唯一的机会,如果错过,我自己都不会原谅自己!'.html</t>
+          <t>吃瓜群众/2021/01/28-辽宁舰的背后丨'这是中华民族唯一的机会,如果错过,我自己都不会原谅自己!'.html</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20210129-赖小民已死,中国扫清屋子再请客</t>
+          <t>赖小民已死,中国扫清屋子再请客</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210129-赖小民已死,中国扫清屋子再请客.html</t>
+          <t>吃瓜群众/2021/01/29-赖小民已死,中国扫清屋子再请客.html</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20210130-岱岱的公开道歉信</t>
+          <t>岱岱的公开道歉信</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210130-岱岱的公开道歉信.html</t>
+          <t>吃瓜群众/2021/01/30-岱岱的公开道歉信.html</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20210131-美国匿名前高官妄称：对抗中国崛起,应该这样做!</t>
+          <t>美国匿名前高官妄称：对抗中国崛起,应该这样做!</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210131-美国匿名前高官妄称：对抗中国崛起,应该这样做!.html</t>
+          <t>吃瓜群众/2021/01/31-美国匿名前高官妄称：对抗中国崛起,应该这样做!.html</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20210202-中国对美重量级演讲,你真的看懂了吗</t>
+          <t>中国对美重量级演讲,你真的看懂了吗</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210202-中国对美重量级演讲,你真的看懂了吗.html</t>
+          <t>吃瓜群众/2021/02/02-中国对美重量级演讲,你真的看懂了吗.html</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20210205-人人影视短评</t>
+          <t>人人影视短评</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210205-人人影视短评.html</t>
+          <t>吃瓜群众/2021/02/05-人人影视短评.html</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20210209-生育率暴跌,如何解决少子化人口问题</t>
+          <t>生育率暴跌,如何解决少子化人口问题</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210209-生育率暴跌,如何解决少子化人口问题.html</t>
+          <t>吃瓜群众/2021/02/09-生育率暴跌,如何解决少子化人口问题.html</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20210220-当喀喇昆仑的雪,落在他们的墓碑上</t>
+          <t>当喀喇昆仑的雪,落在他们的墓碑上</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210220-当喀喇昆仑的雪,落在他们的墓碑上.html</t>
+          <t>吃瓜群众/2021/02/20-当喀喇昆仑的雪,落在他们的墓碑上.html</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20210223-你不知道的省内强藩——宁波篇</t>
+          <t>你不知道的省内强藩——宁波篇</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210223-你不知道的省内强藩——宁波篇.html</t>
+          <t>吃瓜群众/2021/02/23-你不知道的省内强藩——宁波篇.html</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20210227-大连的兴衰</t>
+          <t>大连的兴衰</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210227-大连的兴衰.html</t>
+          <t>吃瓜群众/2021/02/27-大连的兴衰.html</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20210301-周扒皮又回来了</t>
+          <t>周扒皮又回来了</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210301-周扒皮又回来了.html</t>
+          <t>吃瓜群众/2021/03/01-周扒皮又回来了.html</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20210302-内斗无止境,壮哉大江苏!</t>
+          <t>内斗无止境,壮哉大江苏!</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210302-内斗无止境,壮哉大江苏!.html</t>
+          <t>吃瓜群众/2021/03/02-内斗无止境,壮哉大江苏!.html</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20210304-两会前瞻丨中国下半场开启在即</t>
+          <t>两会前瞻丨中国下半场开启在即</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210304-两会前瞻丨中国下半场开启在即.html</t>
+          <t>吃瓜群众/2021/03/04-两会前瞻丨中国下半场开启在即.html</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20210309-中美环保合作,会导致什么</t>
+          <t>中美环保合作,会导致什么</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210309-中美环保合作,会导致什么.html</t>
+          <t>吃瓜群众/2021/03/09-中美环保合作,会导致什么.html</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20210310-普京的接班人,已经定了</t>
+          <t>普京的接班人,已经定了</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210310-普京的接班人,已经定了.html</t>
+          <t>吃瓜群众/2021/03/10-普京的接班人,已经定了.html</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20210311-魔鬼藏在细节,逻辑还原真相!中美阿拉斯加会谈</t>
+          <t>魔鬼藏在细节,逻辑还原真相!中美阿拉斯加会谈</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210311-魔鬼藏在细节,逻辑还原真相!中美阿拉斯加会谈.html</t>
+          <t>吃瓜群众/2021/03/11-魔鬼藏在细节,逻辑还原真相!中美阿拉斯加会谈.html</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3150,15 +3150,15 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20210312-细节</t>
+          <t>细节</t>
         </is>
       </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>吃瓜群众/20210312-细节.html</t>
+          <t>吃瓜群众/2021/03/12-细节.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20201110-国产化,一点也不能放松</t>
+          <t>国产化,一点也不能放松</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>宁南山/20201110-国产化,一点也不能放松.html</t>
+          <t>宁南山/2020/11/10-国产化,一点也不能放松.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20201116-如何看待荣耀从华为独立---一些发散的想法</t>
+          <t>如何看待荣耀从华为独立---一些发散的想法</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>宁南山/20201116-如何看待荣耀从华为独立---一些发散的想法.html</t>
+          <t>宁南山/2020/11/16-如何看待荣耀从华为独立---一些发散的想法.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20201118-RCEP签署--说些题外话,中国,日本和亚洲</t>
+          <t>RCEP签署--说些题外话,中国,日本和亚洲</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>宁南山/20201118-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
+          <t>宁南山/2020/11/18-RCEP签署--说些题外话,中国,日本和亚洲.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20201121-从数据看越南制造对中国的威胁到底有多大</t>
+          <t>从数据看越南制造对中国的威胁到底有多大</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>宁南山/20201121-从数据看越南制造对中国的威胁到底有多大.html</t>
+          <t>宁南山/2020/11/21-从数据看越南制造对中国的威胁到底有多大.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20201127-短文：华为的'新汉阳造'VS洋枪洋炮</t>
+          <t>短文：华为的'新汉阳造'VS洋枪洋炮</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>宁南山/20201127-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
+          <t>宁南山/2020/11/27-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20201129-从出口顺差和逆差来源看中国制造全球地位</t>
+          <t>从出口顺差和逆差来源看中国制造全球地位</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>宁南山/20201129-从出口顺差和逆差来源看中国制造全球地位.html</t>
+          <t>宁南山/2020/11/29-从出口顺差和逆差来源看中国制造全球地位.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20201201-我可以,你不可以--由澳大利亚事件看西方人的心理</t>
+          <t>我可以,你不可以--由澳大利亚事件看西方人的心理</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>宁南山/20201201-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
+          <t>宁南山/2020/12/01-我可以,你不可以--由澳大利亚事件看西方人的心理.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20201205-老老实实搞制造业,会给中国带来意想不到的回报</t>
+          <t>老老实实搞制造业,会给中国带来意想不到的回报</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>宁南山/20201205-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
+          <t>宁南山/2020/12/05-老老实实搞制造业,会给中国带来意想不到的回报.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20201209-中国,西方,苏联--国家的两个道义思考</t>
+          <t>中国,西方,苏联--国家的两个道义思考</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>宁南山/20201209-中国,西方,苏联--国家的两个道义思考.html</t>
+          <t>宁南山/2020/12/09-中国,西方,苏联--国家的两个道义思考.html</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20201212-巨头的使命--从一张中国地图说起</t>
+          <t>巨头的使命--从一张中国地图说起</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>宁南山/20201212-巨头的使命--从一张中国地图说起.html</t>
+          <t>宁南山/2020/12/12-巨头的使命--从一张中国地图说起.html</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20201216-由梁孟松想到深圳的芯片制造业</t>
+          <t>由梁孟松想到深圳的芯片制造业</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>宁南山/20201216-由梁孟松想到深圳的芯片制造业.html</t>
+          <t>宁南山/2020/12/16-由梁孟松想到深圳的芯片制造业.html</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20201220-从两张图看成为发达国家有多难</t>
+          <t>从两张图看成为发达国家有多难</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>宁南山/20201220-从两张图看成为发达国家有多难.html</t>
+          <t>宁南山/2020/12/20-从两张图看成为发达国家有多难.html</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20201225-从数据看中国半导体在全球版图中的位置</t>
+          <t>从数据看中国半导体在全球版图中的位置</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>宁南山/20201225-从数据看中国半导体在全球版图中的位置.html</t>
+          <t>宁南山/2020/12/25-从数据看中国半导体在全球版图中的位置.html</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20201231-新三线建设与年轻人的希望</t>
+          <t>新三线建设与年轻人的希望</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>宁南山/20201231-新三线建设与年轻人的希望.html</t>
+          <t>宁南山/2020/12/31-新三线建设与年轻人的希望.html</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20210101-从2021年初看未来十年的两个三条线</t>
+          <t>从2021年初看未来十年的两个三条线</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>宁南山/20210101-从2021年初看未来十年的两个三条线.html</t>
+          <t>宁南山/2021/01/01-从2021年初看未来十年的两个三条线.html</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20210109-另一个国家</t>
+          <t>另一个国家</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>宁南山/20210109-另一个国家.html</t>
+          <t>宁南山/2021/01/09-另一个国家.html</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
+          <t>反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>宁南山/20210110-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
+          <t>宁南山/2021/01/10-反长臂管辖---简单聊聊_阻断外国法律与措施不当域外适用办法.html</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20210115-2020年两岸半导体制造营收差距拉大</t>
+          <t>2020年两岸半导体制造营收差距拉大</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>宁南山/20210115-2020年两岸半导体制造营收差距拉大.html</t>
+          <t>宁南山/2021/01/15-2020年两岸半导体制造营收差距拉大.html</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20210117-聊聊从东亚产业链和美国产业链想到的</t>
+          <t>聊聊从东亚产业链和美国产业链想到的</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>宁南山/20210117-聊聊从东亚产业链和美国产业链想到的.html</t>
+          <t>宁南山/2021/01/17-聊聊从东亚产业链和美国产业链想到的.html</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
+          <t>从全球2500强企业研发支出看全球竞争情况和产业趋势</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>宁南山/20210123-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
+          <t>宁南山/2021/01/23-从全球2500强企业研发支出看全球竞争情况和产业趋势.html</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20210131-华为手机份额下滑和苹果供应链的隐忧</t>
+          <t>华为手机份额下滑和苹果供应链的隐忧</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>宁南山/20210131-华为手机份额下滑和苹果供应链的隐忧.html</t>
+          <t>宁南山/2021/01/31-华为手机份额下滑和苹果供应链的隐忧.html</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20210207-国产化是漫长的战役</t>
+          <t>国产化是漫长的战役</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>宁南山/20210207-国产化是漫长的战役.html</t>
+          <t>宁南山/2021/02/07-国产化是漫长的战役.html</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20210210-短文：工业化城市化社会的人口是'不可再生'资源</t>
+          <t>短文：工业化城市化社会的人口是'不可再生'资源</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>宁南山/20210210-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
+          <t>宁南山/2021/02/10-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20210211-牛年要来了,今年最后一篇文章说些想法</t>
+          <t>牛年要来了,今年最后一篇文章说些想法</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>宁南山/20210211-牛年要来了,今年最后一篇文章说些想法.html</t>
+          <t>宁南山/2021/02/11-牛年要来了,今年最后一篇文章说些想法.html</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20210218-简单说下2021年预计的几件大事</t>
+          <t>简单说下2021年预计的几件大事</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>宁南山/20210218-简单说下2021年预计的几件大事.html</t>
+          <t>宁南山/2021/02/18-简单说下2021年预计的几件大事.html</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20210221-中国的基建,高科技和印度---由最近的新闻想到的</t>
+          <t>中国的基建,高科技和印度---由最近的新闻想到的</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>宁南山/20210221-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
+          <t>宁南山/2021/02/21-中国的基建,高科技和印度---由最近的新闻想到的.html</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20210226-节能减排的思考：中国人的工业和美国人的生活</t>
+          <t>节能减排的思考：中国人的工业和美国人的生活</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>宁南山/20210226-节能减排的思考：中国人的工业和美国人的生活.html</t>
+          <t>宁南山/2021/02/26-节能减排的思考：中国人的工业和美国人的生活.html</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20210301-短文：由台湾凤梨和芯片想到的</t>
+          <t>短文：由台湾凤梨和芯片想到的</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>宁南山/20210301-短文：由台湾凤梨和芯片想到的.html</t>
+          <t>宁南山/2021/03/01-短文：由台湾凤梨和芯片想到的.html</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
+          <t>读了下过去几年的统计公报,从一张表发现了中国的一些变化</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>宁南山/20210303-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
+          <t>宁南山/2021/03/03-读了下过去几年的统计公报,从一张表发现了中国的一些变化.html</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20210307-从扶贫,修路到半导体</t>
+          <t>从扶贫,修路到半导体</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>宁南山/20210307-从扶贫,修路到半导体.html</t>
+          <t>宁南山/2021/03/07-从扶贫,修路到半导体.html</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>政事堂</t>
+          <t>宁南山</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20201114</t>
+          <t>20210313</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20201114-未来两年经济的确定性与不确定</t>
+          <t>为什么中国现在老被骂</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>政事堂/20201114-未来两年经济的确定性与不确定.html</t>
+          <t>宁南山/2021/03/13-为什么中国现在老被骂.html</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>202011</t>
+          <t>202103</t>
         </is>
       </c>
     </row>
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20201115</t>
+          <t>20201114</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20201115-RCEP签署,为这一刻准备了30年</t>
+          <t>未来两年经济的确定性与不确定</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>政事堂/20201115-RCEP签署,为这一刻准备了30年.html</t>
+          <t>政事堂/2020/11/14-未来两年经济的确定性与不确定.html</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>20201116</t>
+          <t>20201115</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20201116-千万悬赏,谁砍了马云的挚友</t>
+          <t>RCEP签署,为这一刻准备了30年</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>政事堂/20201116-千万悬赏,谁砍了马云的挚友.html</t>
+          <t>政事堂/2020/11/15-RCEP签署,为这一刻准备了30年.html</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>20201117</t>
+          <t>20201116</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20201117-传奇私募被传带走</t>
+          <t>千万悬赏,谁砍了马云的挚友</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>政事堂/20201117-传奇私募被传带走.html</t>
+          <t>政事堂/2020/11/16-千万悬赏,谁砍了马云的挚友.html</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4300,20 +4300,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>20201118</t>
+          <t>20201117</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20201118-莫迪终于给拜登打电话了</t>
+          <t>传奇私募被传带走</t>
         </is>
       </c>
       <c r="E118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>政事堂/20201118-莫迪终于给拜登打电话了.html</t>
+          <t>政事堂/2020/11/17-传奇私募被传带走.html</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20201119</t>
+          <t>20201118</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20201119-谁也救不了的'蛋壳'</t>
+          <t>莫迪终于给拜登打电话了</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>政事堂/20201119-谁也救不了的'蛋壳'.html</t>
+          <t>政事堂/2020/11/18-莫迪终于给拜登打电话了.html</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>20201120</t>
+          <t>20201119</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20201120-坐在宝马里面笑的华晨破产了</t>
+          <t>谁也救不了的'蛋壳'</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>政事堂/20201120-坐在宝马里面笑的华晨破产了.html</t>
+          <t>政事堂/2020/11/19-谁也救不了的'蛋壳'.html</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20201121</t>
+          <t>20201120</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20201121-中国考虑加入CPTPP的考量</t>
+          <t>坐在宝马里面笑的华晨破产了</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>政事堂/20201121-中国考虑加入CPTPP的考量.html</t>
+          <t>政事堂/2020/11/20-坐在宝马里面笑的华晨破产了.html</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20201122</t>
+          <t>20201121</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20201122-零容忍!金融委发了尚方宝剑</t>
+          <t>中国考虑加入CPTPP的考量</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>政事堂/20201122-零容忍!金融委发了尚方宝剑.html</t>
+          <t>政事堂/2020/11/21-中国考虑加入CPTPP的考量.html</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>20201123</t>
+          <t>20201122</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20201123-拜登的国务卿布林肯</t>
+          <t>零容忍!金融委发了尚方宝剑</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>政事堂/20201123-拜登的国务卿布林肯.html</t>
+          <t>政事堂/2020/11/22-零容忍!金融委发了尚方宝剑.html</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>20201124</t>
+          <t>20201123</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20201124-东京地检调查安倍,这只是开始</t>
+          <t>拜登的国务卿布林肯</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>政事堂/20201124-东京地检调查安倍,这只是开始.html</t>
+          <t>政事堂/2020/11/23-拜登的国务卿布林肯.html</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20201125</t>
+          <t>20201124</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20201125-恒大宝能俩野蛮人又栽了一次</t>
+          <t>东京地检调查安倍,这只是开始</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>政事堂/20201125-恒大宝能俩野蛮人又栽了一次.html</t>
+          <t>政事堂/2020/11/24-东京地检调查安倍,这只是开始.html</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20201126</t>
+          <t>20201125</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20201126-投资的抉择</t>
+          <t>恒大宝能俩野蛮人又栽了一次</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>政事堂/20201126-投资的抉择.html</t>
+          <t>政事堂/2020/11/25-恒大宝能俩野蛮人又栽了一次.html</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20201127</t>
+          <t>20201126</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20201127-全球即将爆发的'不讲武德'</t>
+          <t>投资的抉择</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>政事堂/20201127-全球即将爆发的'不讲武德'.html</t>
+          <t>政事堂/2020/11/26-投资的抉择.html</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>20201128</t>
+          <t>20201127</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20201128-刺杀伊朗核之父,特朗普最后的一张牌</t>
+          <t>全球即将爆发的'不讲武德'</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>政事堂/20201128-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
+          <t>政事堂/2020/11/27-全球即将爆发的'不讲武德'.html</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>20201129</t>
+          <t>20201128</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20201129-伊朗刺杀事件中的美国卧底</t>
+          <t>刺杀伊朗核之父,特朗普最后的一张牌</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>政事堂/20201129-伊朗刺杀事件中的美国卧底.html</t>
+          <t>政事堂/2020/11/28-刺杀伊朗核之父,特朗普最后的一张牌.html</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20201130</t>
+          <t>20201129</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20201130-马保国凉凉之必然性分析</t>
+          <t>伊朗刺杀事件中的美国卧底</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>政事堂/20201130-马保国凉凉之必然性分析.html</t>
+          <t>政事堂/2020/11/29-伊朗刺杀事件中的美国卧底.html</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4729,25 +4729,25 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20201202</t>
+          <t>20201130</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20201202-为何要持续去怼澳大利亚</t>
+          <t>马保国凉凉之必然性分析</t>
         </is>
       </c>
       <c r="E131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>政事堂/20201202-为何要持续去怼澳大利亚.html</t>
+          <t>政事堂/2020/11/30-马保国凉凉之必然性分析.html</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>202012</t>
+          <t>202011</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20201202-关于胡锡进的一则短评</t>
+          <t>为何要持续去怼澳大利亚</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>政事堂/20201202-关于胡锡进的一则短评.html</t>
+          <t>政事堂/2020/12/02-为何要持续去怼澳大利亚.html</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4795,20 +4795,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20201203</t>
+          <t>20201202</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20201203-伊万卡成了突破口</t>
+          <t>关于胡锡进的一则短评</t>
         </is>
       </c>
       <c r="E133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>政事堂/20201203-伊万卡成了突破口.html</t>
+          <t>政事堂/2020/12/02-关于胡锡进的一则短评.html</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20201204</t>
+          <t>20201203</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20201204-中国的舆论阵地要升级了</t>
+          <t>伊万卡成了突破口</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>政事堂/20201204-中国的舆论阵地要升级了.html</t>
+          <t>政事堂/2020/12/03-伊万卡成了突破口.html</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4861,20 +4861,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20201205</t>
+          <t>20201204</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20201205-社区团购,将打开潘多拉的魔盒</t>
+          <t>中国的舆论阵地要升级了</t>
         </is>
       </c>
       <c r="E135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>政事堂/20201205-社区团购,将打开潘多拉的魔盒.html</t>
+          <t>政事堂/2020/12/04-中国的舆论阵地要升级了.html</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4894,20 +4894,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20201206</t>
+          <t>20201205</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20201206-沃森生物骂战背后的斗争</t>
+          <t>社区团购,将打开潘多拉的魔盒</t>
         </is>
       </c>
       <c r="E136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>政事堂/20201206-沃森生物骂战背后的斗争.html</t>
+          <t>政事堂/2020/12/05-社区团购,将打开潘多拉的魔盒.html</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20201207</t>
+          <t>20201206</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20201207-伊朗的刺杀,印度的革命</t>
+          <t>沃森生物骂战背后的斗争</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>政事堂/20201207-伊朗的刺杀,印度的革命.html</t>
+          <t>政事堂/2020/12/06-沃森生物骂战背后的斗争.html</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20201208</t>
+          <t>20201207</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20201208-从工行处长落马,到苏宁被传资金链问题</t>
+          <t>伊朗的刺杀,印度的革命</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>政事堂/20201208-从工行处长落马,到苏宁被传资金链问题.html</t>
+          <t>政事堂/2020/12/07-伊朗的刺杀,印度的革命.html</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20201209</t>
+          <t>20201208</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20201209-宁波假名媛碰上了假富二代</t>
+          <t>从工行处长落马,到苏宁被传资金链问题</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>政事堂/20201209-宁波假名媛碰上了假富二代.html</t>
+          <t>政事堂/2020/12/08-从工行处长落马,到苏宁被传资金链问题.html</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20201210</t>
+          <t>20201209</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20201210-张近东把苏宁押给了马云</t>
+          <t>宁波假名媛碰上了假富二代</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>政事堂/20201210-张近东把苏宁押给了马云.html</t>
+          <t>政事堂/2020/12/09-宁波假名媛碰上了假富二代.html</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>20201211</t>
+          <t>20201210</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20201211-今天,特朗普又完成一个'历史性突破'</t>
+          <t>张近东把苏宁押给了马云</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>政事堂/20201211-今天,特朗普又完成一个'历史性突破'.html</t>
+          <t>政事堂/2020/12/10-张近东把苏宁押给了马云.html</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20201212</t>
+          <t>20201211</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20201212-对互联网巨头反垄断的深层理解</t>
+          <t>今天,特朗普又完成一个'历史性突破'</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>政事堂/20201212-对互联网巨头反垄断的深层理解.html</t>
+          <t>政事堂/2020/12/11-今天,特朗普又完成一个'历史性突破'.html</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20201213</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20201213-盲盒、卡片与多巴胺</t>
+          <t>对互联网巨头反垄断的深层理解</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>政事堂/20201213-盲盒、卡片与多巴胺.html</t>
+          <t>政事堂/2020/12/12-对互联网巨头反垄断的深层理解.html</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20201214</t>
+          <t>20201213</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20201214-什么是'需求侧改革'</t>
+          <t>盲盒、卡片与多巴胺</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>政事堂/20201214-什么是'需求侧改革'.html</t>
+          <t>政事堂/2020/12/13-盲盒、卡片与多巴胺.html</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20201215</t>
+          <t>20201214</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20201215-需求侧改革与内循环</t>
+          <t>什么是'需求侧改革'</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>政事堂/20201215-需求侧改革与内循环.html</t>
+          <t>政事堂/2020/12/14-什么是'需求侧改革'.html</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20201216</t>
+          <t>20201215</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20201216-中芯的内斗与消费侧的机遇</t>
+          <t>需求侧改革与内循环</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>政事堂/20201216-中芯的内斗与消费侧的机遇.html</t>
+          <t>政事堂/2020/12/15-需求侧改革与内循环.html</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20201217</t>
+          <t>20201216</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20201217-消费侧改革释放的机会</t>
+          <t>中芯的内斗与消费侧的机遇</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>政事堂/20201217-消费侧改革释放的机会.html</t>
+          <t>政事堂/2020/12/16-中芯的内斗与消费侧的机遇.html</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20201218</t>
+          <t>20201217</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20201218-中央经济工作会议的风向标</t>
+          <t>消费侧改革释放的机会</t>
         </is>
       </c>
       <c r="E148" t="b">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>政事堂/20201218-中央经济工作会议的风向标.html</t>
+          <t>政事堂/2020/12/17-消费侧改革释放的机会.html</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20201219</t>
+          <t>20201218</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20201219-互联网巨头的至暗时刻</t>
+          <t>中央经济工作会议的风向标</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>政事堂/20201219-互联网巨头的至暗时刻.html</t>
+          <t>政事堂/2020/12/18-中央经济工作会议的风向标.html</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20201220</t>
+          <t>20201219</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20201220-从中央经济工作会议,看2021年地产走势</t>
+          <t>互联网巨头的至暗时刻</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>政事堂/20201220-从中央经济工作会议,看2021年地产走势.html</t>
+          <t>政事堂/2020/12/19-互联网巨头的至暗时刻.html</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20201221</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20201221-反垄断与反混业经营</t>
+          <t>从中央经济工作会议,看2021年地产走势</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>政事堂/20201221-反垄断与反混业经营.html</t>
+          <t>政事堂/2020/12/20-从中央经济工作会议,看2021年地产走势.html</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20201222</t>
+          <t>20201221</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20201222-卸任前,特朗普埋了三个棋子</t>
+          <t>反垄断与反混业经营</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>政事堂/20201222-卸任前,特朗普埋了三个棋子.html</t>
+          <t>政事堂/2020/12/21-反垄断与反混业经营.html</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20201223</t>
+          <t>20201222</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20201223-人民日报又提房地产税</t>
+          <t>卸任前,特朗普埋了三个棋子</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>政事堂/20201223-人民日报又提房地产税.html</t>
+          <t>政事堂/2020/12/22-卸任前,特朗普埋了三个棋子.html</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>20201224</t>
+          <t>20201223</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20201224-新一轮双创风口即将到来,谁能抓得住</t>
+          <t>人民日报又提房地产税</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>政事堂/20201224-新一轮双创风口即将到来,谁能抓得住.html</t>
+          <t>政事堂/2020/12/23-人民日报又提房地产税.html</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20201225</t>
+          <t>20201224</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20201225-英法中德美,三场胆小鬼游戏</t>
+          <t>新一轮双创风口即将到来,谁能抓得住</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>政事堂/20201225-英法中德美,三场胆小鬼游戏.html</t>
+          <t>政事堂/2020/12/24-新一轮双创风口即将到来,谁能抓得住.html</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>20201226</t>
+          <t>20201225</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20201226-谁是朋友,谁是敌人</t>
+          <t>英法中德美,三场胆小鬼游戏</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>政事堂/20201226-谁是朋友,谁是敌人.html</t>
+          <t>政事堂/2020/12/25-英法中德美,三场胆小鬼游戏.html</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>20201227</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20201227-反垄断之后,下一步该怎么走</t>
+          <t>谁是朋友,谁是敌人</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>政事堂/20201227-反垄断之后,下一步该怎么走.html</t>
+          <t>政事堂/2020/12/26-谁是朋友,谁是敌人.html</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>20201228</t>
+          <t>20201227</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20201228-下一个二十年</t>
+          <t>反垄断之后,下一步该怎么走</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>政事堂/20201228-下一个二十年.html</t>
+          <t>政事堂/2020/12/27-反垄断之后,下一步该怎么走.html</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>20201229</t>
+          <t>20201228</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20201229-涨价去库存的茅台</t>
+          <t>下一个二十年</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>政事堂/20201229-涨价去库存的茅台.html</t>
+          <t>政事堂/2020/12/28-下一个二十年.html</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>20201230</t>
+          <t>20201229</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20201230-我们,赢了!</t>
+          <t>涨价去库存的茅台</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>政事堂/20201230-我们,赢了!.html</t>
+          <t>政事堂/2020/12/29-涨价去库存的茅台.html</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20201230-揭蛊,是谁写了特斯拉的'黑稿'</t>
+          <t>我们,赢了!</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>政事堂/20201230-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
+          <t>政事堂/2020/12/30-我们,赢了!.html</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20201230</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20201231-2020年就要过去了,我很怀念它</t>
+          <t>揭蛊,是谁写了特斯拉的'黑稿'</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>政事堂/20201231-2020年就要过去了,我很怀念它.html</t>
+          <t>政事堂/2020/12/30-揭蛊,是谁写了特斯拉的'黑稿'.html</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5790,15 +5790,15 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20201231-透过15篇政事堂文章,读懂2020年……</t>
+          <t>2020年就要过去了,我很怀念它</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>政事堂/20201231-透过15篇政事堂文章,读懂2020年…….html</t>
+          <t>政事堂/2020/12/31-2020年就要过去了,我很怀念它.html</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5818,25 +5818,25 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20210101</t>
+          <t>20201231</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20210101-华为VS腾讯,一场短期双输的博弈</t>
+          <t>透过15篇政事堂文章,读懂2020年……</t>
         </is>
       </c>
       <c r="E164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>政事堂/20210101-华为VS腾讯,一场短期双输的博弈.html</t>
+          <t>政事堂/2020/12/31-透过15篇政事堂文章,读懂2020年…….html</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>202012</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20210102</t>
+          <t>20210101</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20210102-山川形便与犬牙相入</t>
+          <t>华为VS腾讯,一场短期双输的博弈</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>政事堂/20210102-山川形便与犬牙相入.html</t>
+          <t>政事堂/2021/01/01-华为VS腾讯,一场短期双输的博弈.html</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20210103</t>
+          <t>20210102</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20210103-温莎银枪小霸王</t>
+          <t>山川形便与犬牙相入</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>政事堂/20210103-温莎银枪小霸王.html</t>
+          <t>政事堂/2021/01/02-山川形便与犬牙相入.html</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>20210104</t>
+          <t>20210103</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20210104-最后的疯狂,强制摘牌三大运营商</t>
+          <t>温莎银枪小霸王</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>政事堂/20210104-最后的疯狂,强制摘牌三大运营商.html</t>
+          <t>政事堂/2021/01/03-温莎银枪小霸王.html</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>20210105</t>
+          <t>20210104</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20210105-拼多多的'临时工'错在哪</t>
+          <t>最后的疯狂,强制摘牌三大运营商</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>政事堂/20210105-拼多多的'临时工'错在哪.html</t>
+          <t>政事堂/2021/01/04-最后的疯狂,强制摘牌三大运营商.html</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>20210106</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20210106-民主党拿下参议院后的影响</t>
+          <t>拼多多的'临时工'错在哪</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>政事堂/20210106-民主党拿下参议院后的影响.html</t>
+          <t>政事堂/2021/01/05-拼多多的'临时工'错在哪.html</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>20210107</t>
+          <t>20210106</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20210107-国会山的陷落</t>
+          <t>民主党拿下参议院后的影响</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>政事堂/20210107-国会山的陷落.html</t>
+          <t>政事堂/2021/01/06-民主党拿下参议院后的影响.html</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>20210108</t>
+          <t>20210107</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20210108-苹果的过去,特斯拉的未来</t>
+          <t>国会山的陷落</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>政事堂/20210108-苹果的过去,特斯拉的未来.html</t>
+          <t>政事堂/2021/01/07-国会山的陷落.html</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20210109</t>
+          <t>20210108</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20210109-封杀推特,特朗普的'社交性死亡'</t>
+          <t>苹果的过去,特斯拉的未来</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>政事堂/20210109-封杀推特,特朗普的'社交性死亡'.html</t>
+          <t>政事堂/2021/01/08-苹果的过去,特斯拉的未来.html</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>20210110</t>
+          <t>20210109</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20210110-特朗普手机变'砖头'了</t>
+          <t>封杀推特,特朗普的'社交性死亡'</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>政事堂/20210110-特朗普手机变'砖头'了.html</t>
+          <t>政事堂/2021/01/09-封杀推特,特朗普的'社交性死亡'.html</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>20210111</t>
+          <t>20210110</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20210111-被'杀人诛心'的特朗普</t>
+          <t>特朗普手机变'砖头'了</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>政事堂/20210111-被'杀人诛心'的特朗普.html</t>
+          <t>政事堂/2021/01/10-特朗普手机变'砖头'了.html</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>20210112</t>
+          <t>20210111</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20210112-新一轮牛市的怎么走</t>
+          <t>被'杀人诛心'的特朗普</t>
         </is>
       </c>
       <c r="E175" t="b">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>政事堂/20210112-新一轮牛市的怎么走.html</t>
+          <t>政事堂/2021/01/11-被'杀人诛心'的特朗普.html</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>20210113</t>
+          <t>20210112</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20210113-马斯克与Paypal的借道入华</t>
+          <t>新一轮牛市的怎么走</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>政事堂/20210113-马斯克与Paypal的借道入华.html</t>
+          <t>政事堂/2021/01/12-新一轮牛市的怎么走.html</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20210114</t>
+          <t>20210113</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20210114-一杯特殊的星巴克</t>
+          <t>马斯克与Paypal的借道入华</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>政事堂/20210114-一杯特殊的星巴克.html</t>
+          <t>政事堂/2021/01/13-马斯克与Paypal的借道入华.html</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>20210115</t>
+          <t>20210114</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20210115-中国迎来了一位女对手</t>
+          <t>一杯特殊的星巴克</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>政事堂/20210115-中国迎来了一位女对手.html</t>
+          <t>政事堂/2021/01/14-一杯特殊的星巴克.html</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>20210116</t>
+          <t>20210115</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20210116-无偿转让好,酱香来养老</t>
+          <t>中国迎来了一位女对手</t>
         </is>
       </c>
       <c r="E179" t="b">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>政事堂/20210116-无偿转让好,酱香来养老.html</t>
+          <t>政事堂/2021/01/15-中国迎来了一位女对手.html</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>20210117</t>
+          <t>20210116</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20210117-两位'小公主'的逆行之旅</t>
+          <t>无偿转让好,酱香来养老</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>政事堂/20210117-两位'小公主'的逆行之旅.html</t>
+          <t>政事堂/2021/01/16-无偿转让好,酱香来养老.html</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>20210118</t>
+          <t>20210117</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20210118-三星太子当庭被捕</t>
+          <t>两位'小公主'的逆行之旅</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>政事堂/20210118-三星太子当庭被捕.html</t>
+          <t>政事堂/2021/01/17-两位'小公主'的逆行之旅.html</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>20210119</t>
+          <t>20210118</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20210119-表演大师武契奇</t>
+          <t>三星太子当庭被捕</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>政事堂/20210119-表演大师武契奇.html</t>
+          <t>政事堂/2021/01/18-三星太子当庭被捕.html</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>20210120</t>
+          <t>20210119</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20210120-告别特朗普</t>
+          <t>表演大师武契奇</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>政事堂/20210120-告别特朗普.html</t>
+          <t>政事堂/2021/01/19-表演大师武契奇.html</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>20210121</t>
+          <t>20210120</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20210121-28人制裁名单,中国送别特朗普</t>
+          <t>告别特朗普</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>政事堂/20210121-28人制裁名单,中国送别特朗普.html</t>
+          <t>政事堂/2021/01/20-告别特朗普.html</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>20210122</t>
+          <t>20210121</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20210122-从上海飙升的房价聊起</t>
+          <t>28人制裁名单,中国送别特朗普</t>
         </is>
       </c>
       <c r="E185" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>政事堂/20210122-从上海飙升的房价聊起.html</t>
+          <t>政事堂/2021/01/21-28人制裁名单,中国送别特朗普.html</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>20210123</t>
+          <t>20210122</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20210123-走向新时代</t>
+          <t>从上海飙升的房价聊起</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>政事堂/20210123-走向新时代.html</t>
+          <t>政事堂/2021/01/22-从上海飙升的房价聊起.html</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20210124</t>
+          <t>20210123</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20210124-俄罗斯全国大抗议背后的黑手</t>
+          <t>走向新时代</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>政事堂/20210124-俄罗斯全国大抗议背后的黑手.html</t>
+          <t>政事堂/2021/01/23-走向新时代.html</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>20210125</t>
+          <t>20210124</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20210125-贾跃亭向左,许家印向右</t>
+          <t>俄罗斯全国大抗议背后的黑手</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>政事堂/20210125-贾跃亭向左,许家印向右.html</t>
+          <t>政事堂/2021/01/24-俄罗斯全国大抗议背后的黑手.html</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6643,20 +6643,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>20210126</t>
+          <t>20210125</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20210126-学术圈为何不能反垄断</t>
+          <t>贾跃亭向左,许家印向右</t>
         </is>
       </c>
       <c r="E189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>政事堂/20210126-学术圈为何不能反垄断.html</t>
+          <t>政事堂/2021/01/25-贾跃亭向左,许家印向右.html</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6676,20 +6676,20 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>20210127</t>
+          <t>20210126</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20210127-废柴们如何收割华尔街大佬</t>
+          <t>学术圈为何不能反垄断</t>
         </is>
       </c>
       <c r="E190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>政事堂/20210127-废柴们如何收割华尔街大佬.html</t>
+          <t>政事堂/2021/01/26-学术圈为何不能反垄断.html</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>20210128</t>
+          <t>20210127</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20210128-资本割韭菜的套路</t>
+          <t>废柴们如何收割华尔街大佬</t>
         </is>
       </c>
       <c r="E191" t="b">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>政事堂/20210128-资本割韭菜的套路.html</t>
+          <t>政事堂/2021/01/27-废柴们如何收割华尔街大佬.html</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>20210129</t>
+          <t>20210128</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20210129-从海航破产说起</t>
+          <t>资本割韭菜的套路</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>政事堂/20210129-从海航破产说起.html</t>
+          <t>政事堂/2021/01/28-资本割韭菜的套路.html</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>20210130</t>
+          <t>20210129</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20210130-英国老佛爷要抢先来割韭菜了</t>
+          <t>从海航破产说起</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>政事堂/20210130-英国老佛爷要抢先来割韭菜了.html</t>
+          <t>政事堂/2021/01/29-从海航破产说起.html</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>20210131</t>
+          <t>20210130</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20210131-基金要变天了......</t>
+          <t>英国老佛爷要抢先来割韭菜了</t>
         </is>
       </c>
       <c r="E194" t="b">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>政事堂/20210131-基金要变天了.......html</t>
+          <t>政事堂/2021/01/30-英国老佛爷要抢先来割韭菜了.html</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20210201</t>
+          <t>20210131</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20210201-缅甸政变,下一步呢</t>
+          <t>基金要变天了......</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>政事堂/20210201-缅甸政变,下一步呢.html</t>
+          <t>政事堂/2021/01/31-基金要变天了.......html</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>202102</t>
+          <t>202101</t>
         </is>
       </c>
     </row>
@@ -6874,20 +6874,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>20210202</t>
+          <t>20210201</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20210202-调控背后的定价权之争</t>
+          <t>缅甸政变,下一步呢</t>
         </is>
       </c>
       <c r="E196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>政事堂/20210202-调控背后的定价权之争.html</t>
+          <t>政事堂/2021/02/01-缅甸政变,下一步呢.html</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6907,20 +6907,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>20210203</t>
+          <t>20210202</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20210203-告别人人影视</t>
+          <t>调控背后的定价权之争</t>
         </is>
       </c>
       <c r="E197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>政事堂/20210203-告别人人影视.html</t>
+          <t>政事堂/2021/02/02-调控背后的定价权之争.html</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>20210204</t>
+          <t>20210203</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20210204-短视频的机制</t>
+          <t>告别人人影视</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>政事堂/20210204-短视频的机制.html</t>
+          <t>政事堂/2021/02/03-告别人人影视.html</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>20210205</t>
+          <t>20210204</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20210205-拜登的外交与A股的改革</t>
+          <t>短视频的机制</t>
         </is>
       </c>
       <c r="E199" t="b">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>政事堂/20210205-拜登的外交与A股的改革.html</t>
+          <t>政事堂/2021/02/04-短视频的机制.html</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>20210206</t>
+          <t>20210205</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20210206-漫谈影视文化的知识产权与垄断</t>
+          <t>拜登的外交与A股的改革</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>政事堂/20210206-漫谈影视文化的知识产权与垄断.html</t>
+          <t>政事堂/2021/02/05-拜登的外交与A股的改革.html</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7039,20 +7039,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>20210207</t>
+          <t>20210206</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20210207-抖音大战腾讯,中国互联网'二战'爆发!</t>
+          <t>漫谈影视文化的知识产权与垄断</t>
         </is>
       </c>
       <c r="E201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>政事堂/20210207-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
+          <t>政事堂/2021/02/06-漫谈影视文化的知识产权与垄断.html</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7072,20 +7072,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>20210208</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20210208-知识产权秩序与短视频革命</t>
+          <t>抖音大战腾讯,中国互联网'二战'爆发!</t>
         </is>
       </c>
       <c r="E202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>政事堂/20210208-知识产权秩序与短视频革命.html</t>
+          <t>政事堂/2021/02/07-抖音大战腾讯,中国互联网'二战'爆发!.html</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>20210210</t>
+          <t>20210208</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20210210-拼团的名媛与美国的航母</t>
+          <t>知识产权秩序与短视频革命</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>政事堂/20210210-拼团的名媛与美国的航母.html</t>
+          <t>政事堂/2021/02/08-知识产权秩序与短视频革命.html</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7138,20 +7138,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>20210212</t>
+          <t>20210210</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20210212-牛年的新秩序</t>
+          <t>拼团的名媛与美国的航母</t>
         </is>
       </c>
       <c r="E204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>政事堂/20210212-牛年的新秩序.html</t>
+          <t>政事堂/2021/02/10-拼团的名媛与美国的航母.html</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7171,20 +7171,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>20210213</t>
+          <t>20210212</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20210213-马斯克的神化与革命</t>
+          <t>牛年的新秩序</t>
         </is>
       </c>
       <c r="E205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>政事堂/20210213-马斯克的神化与革命.html</t>
+          <t>政事堂/2021/02/12-牛年的新秩序.html</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7204,20 +7204,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>20210215</t>
+          <t>20210213</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20210215-低生育率的原因</t>
+          <t>马斯克的神化与革命</t>
         </is>
       </c>
       <c r="E206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>政事堂/20210215-低生育率的原因.html</t>
+          <t>政事堂/2021/02/13-马斯克的神化与革命.html</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7237,20 +7237,20 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>20210216</t>
+          <t>20210215</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20210216-一代版本一代神</t>
+          <t>低生育率的原因</t>
         </is>
       </c>
       <c r="E207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>政事堂/20210216-一代版本一代神.html</t>
+          <t>政事堂/2021/02/15-低生育率的原因.html</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>20210217</t>
+          <t>20210216</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20210217-马斯克、宗教与黑客帝国</t>
+          <t>一代版本一代神</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>政事堂/20210217-马斯克、宗教与黑客帝国.html</t>
+          <t>政事堂/2021/02/16-一代版本一代神.html</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>20210218</t>
+          <t>20210217</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20210218-品酒师入围院士,在侮辱谁</t>
+          <t>马斯克、宗教与黑客帝国</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>政事堂/20210218-品酒师入围院士,在侮辱谁.html</t>
+          <t>政事堂/2021/02/17-马斯克、宗教与黑客帝国.html</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>20210219</t>
+          <t>20210218</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20210219-今天,要大张旗鼓的纪念英雄</t>
+          <t>品酒师入围院士,在侮辱谁</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>政事堂/20210219-今天,要大张旗鼓的纪念英雄.html</t>
+          <t>政事堂/2021/02/18-品酒师入围院士,在侮辱谁.html</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7369,20 +7369,20 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>20210221</t>
+          <t>20210219</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20210221-应该用《英烈法》保护我们的英雄</t>
+          <t>今天,要大张旗鼓的纪念英雄</t>
         </is>
       </c>
       <c r="E211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>政事堂/20210221-应该用《英烈法》保护我们的英雄.html</t>
+          <t>政事堂/2021/02/19-今天,要大张旗鼓的纪念英雄.html</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7407,15 +7407,15 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20210221-资本大佬们又要回来了</t>
+          <t>应该用《英烈法》保护我们的英雄</t>
         </is>
       </c>
       <c r="E212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>政事堂/20210221-资本大佬们又要回来了.html</t>
+          <t>政事堂/2021/02/21-应该用《英烈法》保护我们的英雄.html</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>20210223</t>
+          <t>20210221</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20210223-抱团基金的走向</t>
+          <t>资本大佬们又要回来了</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>政事堂/20210223-抱团基金的走向.html</t>
+          <t>政事堂/2021/02/21-资本大佬们又要回来了.html</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>20210224</t>
+          <t>20210223</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20210224-印花税打崩了抱团基金</t>
+          <t>抱团基金的走向</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>政事堂/20210224-印花税打崩了抱团基金.html</t>
+          <t>政事堂/2021/02/23-抱团基金的走向.html</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>20210225</t>
+          <t>20210224</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20210225-CNN放出'最高机密',中东王爷们要吐血了</t>
+          <t>印花税打崩了抱团基金</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>政事堂/20210225-CNN放出'最高机密',中东王爷们要吐血了.html</t>
+          <t>政事堂/2021/02/24-印花税打崩了抱团基金.html</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20210225-马斯克VS神,巨头的归来</t>
+          <t>CNN放出'最高机密',中东王爷们要吐血了</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>政事堂/20210225-马斯克VS神,巨头的归来.html</t>
+          <t>政事堂/2021/02/25-CNN放出'最高机密',中东王爷们要吐血了.html</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>20210226</t>
+          <t>20210225</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20210226-不讲武德,拜登突袭叙利亚</t>
+          <t>马斯克VS神,巨头的归来</t>
         </is>
       </c>
       <c r="E217" t="b">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>政事堂/20210226-不讲武德,拜登突袭叙利亚.html</t>
+          <t>政事堂/2021/02/25-马斯克VS神,巨头的归来.html</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>20210227</t>
+          <t>20210226</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20210227-'第一村'的华西垮不了</t>
+          <t>不讲武德,拜登突袭叙利亚</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>政事堂/20210227-'第一村'的华西垮不了.html</t>
+          <t>政事堂/2021/02/26-不讲武德,拜登突袭叙利亚.html</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>20210228</t>
+          <t>20210227</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20210228-'大空头'巴菲特的唱空</t>
+          <t>'第一村'的华西垮不了</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>政事堂/20210228-'大空头'巴菲特的唱空.html</t>
+          <t>政事堂/2021/02/27-'第一村'的华西垮不了.html</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>20210301</t>
+          <t>20210228</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20210301-凤梨与稀土</t>
+          <t>'大空头'巴菲特的唱空</t>
         </is>
       </c>
       <c r="E220" t="b">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>政事堂/20210301-凤梨与稀土.html</t>
+          <t>政事堂/2021/02/28-'大空头'巴菲特的唱空.html</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>202103</t>
+          <t>202102</t>
         </is>
       </c>
     </row>
@@ -7699,12 +7699,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>20210302</t>
+          <t>20210301</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20210302-'口头加息'与'进一步加征印花税'</t>
+          <t>凤梨与稀土</t>
         </is>
       </c>
       <c r="E221" t="b">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>政事堂/20210302-'口头加息'与'进一步加征印花税'.html</t>
+          <t>政事堂/2021/03/01-凤梨与稀土.html</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7732,20 +7732,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>20210303</t>
+          <t>20210302</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20210303-破局：从世界工厂到世界发动机</t>
+          <t>'口头加息'与'进一步加征印花税'</t>
         </is>
       </c>
       <c r="E222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>政事堂/20210303-破局：从世界工厂到世界发动机.html</t>
+          <t>政事堂/2021/03/02-'口头加息'与'进一步加征印花税'.html</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>20210304</t>
+          <t>20210303</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20210304-炒币与X茅的起源</t>
+          <t>破局：从世界工厂到世界发动机</t>
         </is>
       </c>
       <c r="E223" t="b">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>政事堂/20210304-炒币与X茅的起源.html</t>
+          <t>政事堂/2021/03/03-破局：从世界工厂到世界发动机.html</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -7798,20 +7798,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>20210305</t>
+          <t>20210304</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20210305-阳谋推恩令</t>
+          <t>炒币与X茅的起源</t>
         </is>
       </c>
       <c r="E224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>政事堂/20210305-阳谋推恩令.html</t>
+          <t>政事堂/2021/03/04-炒币与X茅的起源.html</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -7831,20 +7831,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>20210306</t>
+          <t>20210305</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20210306-拜登、白酒与新能源</t>
+          <t>阳谋推恩令</t>
         </is>
       </c>
       <c r="E225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>政事堂/20210306-拜登、白酒与新能源.html</t>
+          <t>政事堂/2021/03/05-阳谋推恩令.html</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>20210307</t>
+          <t>20210306</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20210307-拜登、旧巨头与新神</t>
+          <t>拜登、白酒与新能源</t>
         </is>
       </c>
       <c r="E226" t="b">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>政事堂/20210307-拜登、旧巨头与新神.html</t>
+          <t>政事堂/2021/03/06-拜登、白酒与新能源.html</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>20210308</t>
+          <t>20210307</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20210308-抱团股的梦想与贾跃亭的窒息</t>
+          <t>拜登、旧巨头与新神</t>
         </is>
       </c>
       <c r="E227" t="b">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>政事堂/20210308-抱团股的梦想与贾跃亭的窒息.html</t>
+          <t>政事堂/2021/03/07-拜登、旧巨头与新神.html</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>20210309</t>
+          <t>20210308</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20210309-救市的国家队与撤退的集结号</t>
+          <t>抱团股的梦想与贾跃亭的窒息</t>
         </is>
       </c>
       <c r="E228" t="b">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>政事堂/20210309-救市的国家队与撤退的集结号.html</t>
+          <t>政事堂/2021/03/08-抱团股的梦想与贾跃亭的窒息.html</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>20210310</t>
+          <t>20210309</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20210310-中美的阿拉斯加会谈</t>
+          <t>救市的国家队与撤退的集结号</t>
         </is>
       </c>
       <c r="E229" t="b">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>政事堂/20210310-中美的阿拉斯加会谈.html</t>
+          <t>政事堂/2021/03/09-救市的国家队与撤退的集结号.html</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>20210311</t>
+          <t>20210310</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20210311-中美对话新机制的建立</t>
+          <t>中美的阿拉斯加会谈</t>
         </is>
       </c>
       <c r="E230" t="b">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>政事堂/20210311-中美对话新机制的建立.html</t>
+          <t>政事堂/2021/03/10-中美的阿拉斯加会谈.html</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -8029,23 +8029,56 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
+          <t>20210311</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>中美对话新机制的建立</t>
+        </is>
+      </c>
+      <c r="E231" t="b">
+        <v>1</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>政事堂/2021/03/11-中美对话新机制的建立.html</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>202103</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>政事堂</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
           <t>20210312</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>20210312-整顿校外培训,'减负'为了谁</t>
-        </is>
-      </c>
-      <c r="E231" t="b">
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>整顿校外培训,'减负'为了谁</t>
+        </is>
+      </c>
+      <c r="E232" t="b">
         <v>0</v>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>政事堂/20210312-整顿校外培训,'减负'为了谁.html</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>政事堂/2021/03/12-整顿校外培训,'减负'为了谁.html</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
         <is>
           <t>202103</t>
         </is>

--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="E232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>

--- a/data/list.xlsx
+++ b/data/list.xlsx
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>美国匿名前高官妄称：对抗中国崛起,应该这样做!</t>
+          <t>美国匿名前高官妄称_对抗中国崛起,应该这样做!</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>吃瓜群众/2021/01/31-美国匿名前高官妄称：对抗中国崛起,应该这样做!.html</t>
+          <t>吃瓜群众/2021/01/31-美国匿名前高官妄称_对抗中国崛起,应该这样做!.html</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>短文：华为的'新汉阳造'VS洋枪洋炮</t>
+          <t>短文_华为的'新汉阳造'VS洋枪洋炮</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>宁南山/2020/11/27-短文：华为的'新汉阳造'VS洋枪洋炮.html</t>
+          <t>宁南山/2020/11/27-短文_华为的'新汉阳造'VS洋枪洋炮.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>短文：工业化城市化社会的人口是'不可再生'资源</t>
+          <t>短文_工业化城市化社会的人口是'不可再生'资源</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>宁南山/2021/02/10-短文：工业化城市化社会的人口是'不可再生'资源.html</t>
+          <t>宁南山/2021/02/10-短文_工业化城市化社会的人口是'不可再生'资源.html</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>节能减排的思考：中国人的工业和美国人的生活</t>
+          <t>节能减排的思考_中国人的工业和美国人的生活</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>宁南山/2021/02/26-节能减排的思考：中国人的工业和美国人的生活.html</t>
+          <t>宁南山/2021/02/26-节能减排的思考_中国人的工业和美国人的生活.html</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>短文：由台湾凤梨和芯片想到的</t>
+          <t>短文_由台湾凤梨和芯片想到的</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>宁南山/2021/03/01-短文：由台湾凤梨和芯片想到的.html</t>
+          <t>宁南山/2021/03/01-短文_由台湾凤梨和芯片想到的.html</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>破局：从世界工厂到世界发动机</t>
+          <t>破局_从世界工厂到世界发动机</t>
         </is>
       </c>
       <c r="E223" t="b">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>政事堂/2021/03/03-破局：从世界工厂到世界发动机.html</t>
+          <t>政事堂/2021/03/03-破局_从世界工厂到世界发动机.html</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
